--- a/Result/checkGreat.xlsx
+++ b/Result/checkGreat.xlsx
@@ -17343,7 +17343,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -17363,184 +17363,184 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>-11.68</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>-11.68</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>2025-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>2025-07-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>-3.61</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>-3.34</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>98.03999999999999</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>101.425</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>102.356</t>
+        </is>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>-135.81</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>19.14893617021276</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>8.23</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>2025-06-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2025-06-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>2025-07-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2025-09-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>-3.61</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>-3.34</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>98.03999999999999</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>101.425</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>102.356</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>-135.81</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="AP47" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>19.14893617021276</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr">
-        <is>
-          <t>8.23</t>
-        </is>
-      </c>
-      <c r="AT47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU47" t="inlineStr">
         <is>
           <t>250416373.6</t>
@@ -17593,67 +17593,67 @@
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.243628495975055</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.93608575876562</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.47688511853321</t>
         </is>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BK47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BL47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.47</t>
         </is>
       </c>
       <c r="BM47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.38%</t>
         </is>
       </c>
       <c r="BN47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.65%</t>
         </is>
       </c>
       <c r="BO47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.78</t>
         </is>
       </c>
       <c r="BP47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19930</t>
         </is>
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
         </is>
       </c>
       <c r="BR47" t="inlineStr">
@@ -17668,12 +17668,12 @@
       </c>
       <c r="BT47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BU47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
         </is>
       </c>
     </row>
@@ -17710,7 +17710,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -17730,184 +17730,184 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>-0.81</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>7.29</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>7.29</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>1235.0</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>1105.0</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>1325.0</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>1255.0</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>5.84</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>1181.0</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>1193.0</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>1225.9</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>36.30</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>-12.17</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>-19.10</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>96.66666666666667</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>96.32478632478633</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>9.39</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-07-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>1235.0</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>1105.0</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>1325.0</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>1255.0</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>5.84</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>-2.68</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>1181.0</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>1193.0</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>1225.9</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>36.30</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>-12.17</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>-19.10</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>96.66666666666667</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>96.32478632478633</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>9.39</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU48" t="inlineStr">
         <is>
           <t>5107509521.0</t>
@@ -17960,67 +17960,67 @@
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.685556694868136</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.66458684921591</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.79701639298051</t>
         </is>
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BK48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="BL48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36.38</t>
         </is>
       </c>
       <c r="BM48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.34%</t>
         </is>
       </c>
       <c r="BN48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.63%</t>
         </is>
       </c>
       <c r="BO48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.78</t>
         </is>
       </c>
       <c r="BP48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>433466</t>
         </is>
       </c>
       <c r="BQ48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>銅箔基板(CCL)56.09%、黏合片42.56%、多層壓合板0.74%、其他0.61% (2024年)</t>
         </is>
       </c>
       <c r="BR48" t="inlineStr">
@@ -18035,12 +18035,12 @@
       </c>
       <c r="BT48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103.29</t>
         </is>
       </c>
       <c r="BU48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 印刷電路板 - 銅箔基板</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -18202,12 +18202,12 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -18332,62 +18332,62 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.272573996457884</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64.81586779784107</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46.02020999447999</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BK49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BL49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="BM49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.56%</t>
         </is>
       </c>
       <c r="BN49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.70%</t>
         </is>
       </c>
       <c r="BO49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.78</t>
         </is>
       </c>
       <c r="BP49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204605</t>
         </is>
       </c>
       <c r="BQ49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>印刷電路板(PCB)100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR49" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="BT49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="BU49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
     </row>
@@ -18444,7 +18444,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -18464,12 +18464,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -18569,12 +18569,12 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -18694,67 +18694,67 @@
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.35448292875888</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1204.911455451024</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1250.255233534527</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BK50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BL50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BM50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.60%</t>
         </is>
       </c>
       <c r="BN50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.87%</t>
         </is>
       </c>
       <c r="BO50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="BP50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="BQ50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>積體電路(IC)100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR50" t="inlineStr">
@@ -18769,12 +18769,12 @@
       </c>
       <c r="BT50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="BU50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC設計</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -18831,12 +18831,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -18936,12 +18936,12 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>147</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -19066,62 +19066,62 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.51400027045762</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172.2532486019545</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>147.5078841276695</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BK51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108.43</t>
         </is>
       </c>
       <c r="BL51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="BM51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.93%</t>
         </is>
       </c>
       <c r="BN51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.39%</t>
         </is>
       </c>
       <c r="BO51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BP51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>545967</t>
         </is>
       </c>
       <c r="BQ51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>網路交換器57.00%、網路應用設備36.00%、網路接取設備4.00%、其他3.00% (2024年)</t>
         </is>
       </c>
       <c r="BR51" t="inlineStr">
@@ -19136,12 +19136,12 @@
       </c>
       <c r="BT51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.09</t>
         </is>
       </c>
       <c r="BU51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
     </row>

--- a/Result/checkGreat.xlsx
+++ b/Result/checkGreat.xlsx
@@ -2948,12 +2948,12 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>97.97999999999999</t>
+          <t>97.98</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>90.44749999999999</t>
+          <t>90.4475</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">

--- a/Result/checkGreat.xlsx
+++ b/Result/checkGreat.xlsx
@@ -1316,7 +1316,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1786,7 +1786,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3112,7 +3112,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3554,7 +3554,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5767,7 +5767,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6212,7 +6212,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6654,7 +6654,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7096,7 +7096,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9325,7 +9325,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9768,7 +9768,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10652,7 +10652,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11094,7 +11094,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11536,7 +11536,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12866,7 +12866,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -13753,7 +13753,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -14197,7 +14197,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -15084,7 +15084,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15527,7 +15527,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -16417,7 +16417,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -17746,7 +17746,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -19072,7 +19072,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -19514,7 +19514,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19956,7 +19956,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -20398,7 +20398,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -21730,7 +21730,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -22172,7 +22172,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -22614,7 +22614,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>【d1】;【d2】;【x】看好</t>
+          <t>【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/Result/checkGreat.xlsx
+++ b/Result/checkGreat.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ52"/>
+  <dimension ref="A1:CJ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18189,52 +18189,52 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>24.527</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-43.75</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -18244,37 +18244,37 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2025-08-08 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2025-06-25 00:00:00</t>
+          <t>2025-10-09 00:00:00</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>2025-10-29 00:00:00</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -18284,12 +18284,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -18299,12 +18299,12 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -18314,12 +18314,12 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -18329,142 +18329,142 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>貿易百貨｜下游｜零售通路</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>83.42</t>
+          <t>77.97999999999999</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>82.69</t>
+          <t>78.52</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>85.59</t>
+          <t>79.52</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>78.67</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>-32.60</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>-144.98</t>
+          <t>-112.18</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>1337.884285714286</t>
+          <t>27804512.13053098</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1898661.0</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>1389279.8</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>304.0</t>
+          <t>1786221.5</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>741.74</t>
+          <t>6531058.28</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>-133</t>
+          <t>-396941</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>-74.98634182456088</t>
+          <t>-358994.5231914897</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>-105.8619756960023</t>
+          <t>-251823.002984701</t>
         </is>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>1898661.0</t>
         </is>
       </c>
       <c r="BE41" t="inlineStr">
@@ -18474,62 +18474,62 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>2025/05/20</t>
+          <t>2025/10/13</t>
         </is>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.30</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>振宇五金</t>
+          <t>世界健身-KY</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
         <is>
-          <t>振宇五金</t>
+          <t>世界健身-KY</t>
         </is>
       </c>
       <c r="BK41" t="inlineStr">
         <is>
-          <t>居家生活</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="BL41" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="BM41" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BN41" t="inlineStr">
         <is>
-          <t>6.109136547243637</t>
+          <t>-1.721709673216402</t>
         </is>
       </c>
       <c r="BO41" t="inlineStr">
         <is>
-          <t>7.959953429229061</t>
+          <t>14.29347943729451</t>
         </is>
       </c>
       <c r="BP41" t="inlineStr">
         <is>
-          <t>6.662021085486349</t>
+          <t>11.70837690335246</t>
         </is>
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
@@ -18539,87 +18539,87 @@
       </c>
       <c r="BS41" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="BT41" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="BU41" t="inlineStr">
         <is>
-          <t>27.64</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>27.94</t>
         </is>
       </c>
       <c r="BW41" t="inlineStr">
         <is>
-          <t>38.86%</t>
+          <t>16.71%</t>
         </is>
       </c>
       <c r="BX41" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="BY41" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BZ41" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="CA41" t="inlineStr">
         <is>
-          <t>水電油漆48.67%、工具19.23%、居家五金16.43%、建築土木15.67% (2024年)</t>
+          <t>會員服務49.66%、教練課程49.14%、其他1.08%、權利金收入0.12% (2024年)</t>
         </is>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>振宇五金-居家生活-上櫃</t>
+          <t>世界健身-KY-運動休閒-上市</t>
         </is>
       </c>
       <c r="CC41" t="inlineStr">
         <is>
-          <t>居家生活右下上櫃</t>
+          <t>運動休閒右下上市</t>
         </is>
       </c>
       <c r="CD41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CE41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CF41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CG41" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH41" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="CI41" t="inlineStr">
         <is>
-          <t>** 貿易百貨 - 零售通路</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CJ41" t="inlineStr">
@@ -18631,22 +18631,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>24.527</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -18656,7 +18656,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-32.15</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -18686,37 +18686,37 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-08-06 00:00:00</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-06-30 00:00:00</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-10-29 00:00:00</t>
+          <t>2025-07-03 00:00:00</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -18726,12 +18726,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-21.22</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -18756,12 +18756,12 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -18771,142 +18771,142 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>食品｜下游｜餐飲連鎖</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>77.97999999999999</t>
+          <t>121.2</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>78.52</t>
+          <t>121.6</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>79.52</t>
+          <t>120.31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>78.67</t>
+          <t>130.22</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>-32.60</t>
+          <t>160.68</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>-112.18</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/10/29</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>27804512.13053098</t>
+          <t>11792.2828854314</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>1898661.0</t>
+          <t>1895.0</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>1389279.8</t>
+          <t>2185.2</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>1786221.5</t>
+          <t>3220.5</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>6531058.28</t>
+          <t>8493.5</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>-396941</t>
+          <t>-1035</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>-358994.5231914897</t>
+          <t>-1102.172914967108</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>-251823.002984701</t>
+          <t>-1284.983275308958</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>1898661.0</t>
+          <t>1895.0</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
@@ -18916,62 +18916,62 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>-6.30</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>世界健身-KY</t>
+          <t>揚秦</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr">
         <is>
-          <t>世界健身-KY</t>
+          <t>揚秦</t>
         </is>
       </c>
       <c r="BK42" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>觀光事業</t>
         </is>
       </c>
       <c r="BL42" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="BM42" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BN42" t="inlineStr">
         <is>
-          <t>-1.721709673216402</t>
+          <t>4.467426697560563</t>
         </is>
       </c>
       <c r="BO42" t="inlineStr">
         <is>
-          <t>14.29347943729451</t>
+          <t>19.64778487987657</t>
         </is>
       </c>
       <c r="BP42" t="inlineStr">
         <is>
-          <t>11.70837690335246</t>
+          <t>19.87904437844922</t>
         </is>
       </c>
       <c r="BQ42" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR42" t="inlineStr">
@@ -18981,87 +18981,87 @@
       </c>
       <c r="BS42" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="BT42" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU42" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="BV42" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="BW42" t="inlineStr">
         <is>
-          <t>16.71%</t>
+          <t>27.53%</t>
         </is>
       </c>
       <c r="BX42" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>10.48%</t>
         </is>
       </c>
       <c r="BY42" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="BZ42" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="CA42" t="inlineStr">
         <is>
-          <t>會員服務49.66%、教練課程49.14%、其他1.08%、權利金收入0.12% (2024年)</t>
+          <t>商品銷售73.51%、門市餐飲18.61%、專案收入7.69%、其他0.19% (2024年)</t>
         </is>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>世界健身-KY-運動休閒-上市</t>
+          <t>揚秦-觀光事業-上櫃</t>
         </is>
       </c>
       <c r="CC42" t="inlineStr">
         <is>
-          <t>運動休閒右下上市</t>
+          <t>觀光事業平上櫃</t>
         </is>
       </c>
       <c r="CD42" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CE42" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CF42" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CG42" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH42" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="CI42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>** 食品 - 餐飲連鎖</t>
         </is>
       </c>
       <c r="CJ42" t="inlineStr">
@@ -19073,22 +19073,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -19113,12 +19113,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-32.15</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -19128,37 +19128,37 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2025-08-06 00:00:00</t>
+          <t>2025-09-09 00:00:00</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2025-09-01 00:00:00</t>
+          <t>2025-09-18 00:00:00</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2025-06-30 00:00:00</t>
+          <t>2025-07-29 00:00:00</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2025-09-02 00:00:00</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -19168,12 +19168,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -19183,12 +19183,12 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>-21.22</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -19198,12 +19198,12 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -19218,137 +19218,137 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>121.2</t>
+          <t>66.38</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>121.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>120.31</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>130.22</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>160.68</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>-99.31</t>
+          <t>-144.35</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/11/21</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>11792.2828854314</t>
+          <t>2888.12</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>1895.0</t>
+          <t>917.0</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>2185.2</t>
+          <t>759.2</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>3220.5</t>
+          <t>665.4</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>8493.5</t>
+          <t>1352.34</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>-1035</t>
+          <t>93</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>-1102.172914967108</t>
+          <t>-112.4300470946464</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>-1284.983275308958</t>
+          <t>-32.40920372952633</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>1895.0</t>
+          <t>917.0</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
@@ -19358,27 +19358,27 @@
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>揚秦</t>
+          <t>王座</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
         <is>
-          <t>揚秦</t>
+          <t>王座</t>
         </is>
       </c>
       <c r="BK43" t="inlineStr">
@@ -19393,27 +19393,27 @@
       </c>
       <c r="BM43" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN43" t="inlineStr">
         <is>
-          <t>4.467426697560563</t>
+          <t>2.951067012747893</t>
         </is>
       </c>
       <c r="BO43" t="inlineStr">
         <is>
-          <t>19.64778487987657</t>
+          <t>39.39682484721525</t>
         </is>
       </c>
       <c r="BP43" t="inlineStr">
         <is>
-          <t>19.87904437844922</t>
+          <t>26.17541857990816</t>
         </is>
       </c>
       <c r="BQ43" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR43" t="inlineStr">
@@ -19423,32 +19423,32 @@
       </c>
       <c r="BS43" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BT43" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="BU43" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BV43" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BW43" t="inlineStr">
         <is>
-          <t>27.53%</t>
+          <t>50.58%</t>
         </is>
       </c>
       <c r="BX43" t="inlineStr">
         <is>
-          <t>10.48%</t>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="BY43" t="inlineStr">
@@ -19458,17 +19458,17 @@
       </c>
       <c r="BZ43" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="CA43" t="inlineStr">
         <is>
-          <t>商品銷售73.51%、門市餐飲18.61%、專案收入7.69%、其他0.19% (2024年)</t>
+          <t>餐飲95.78%、其他4.22% (2024年)</t>
         </is>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>揚秦-觀光事業-上櫃</t>
+          <t>王座-觀光事業-上櫃</t>
         </is>
       </c>
       <c r="CC43" t="inlineStr">
@@ -19478,27 +19478,27 @@
       </c>
       <c r="CD43" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE43" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CF43" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CG43" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH43" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="CI43" t="inlineStr">
@@ -19520,17 +19520,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>128.343</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -19570,37 +19570,37 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2025-05-23 00:00:00</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2025-09-18 00:00:00</t>
+          <t>2025-06-09 00:00:00</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2025-07-29 00:00:00</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2025-09-02 00:00:00</t>
+          <t>2025-03-13 00:00:00</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -19610,12 +19610,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>233.5</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -19625,12 +19625,12 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-13.77</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -19640,12 +19640,12 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -19660,27 +19660,27 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
@@ -19690,107 +19690,107 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>66.38</t>
+          <t>213.4</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>214.78</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>219.19</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>220.92</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>-144.35</t>
+          <t>-106.67</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2025/11/21</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>2888.12</t>
+          <t>465563659.8182461</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>917.0</t>
+          <t>27360978.0</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>759.2</t>
+          <t>39383506.6</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>665.4</t>
+          <t>37418389.3</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>1352.34</t>
+          <t>81902030.2</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1965117</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>-112.4300470946464</t>
+          <t>-8794209.991249312</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>-32.40920372952633</t>
+          <t>-8020093.736558624</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>917.0</t>
+          <t>27360978.0</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
@@ -19800,27 +19800,27 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>228.5</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/09/25</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>王座</t>
+          <t>王品</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr">
         <is>
-          <t>王座</t>
+          <t>王品</t>
         </is>
       </c>
       <c r="BK44" t="inlineStr">
@@ -19830,32 +19830,32 @@
       </c>
       <c r="BL44" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="BM44" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN44" t="inlineStr">
         <is>
-          <t>2.951067012747893</t>
+          <t>13.0908532754338</t>
         </is>
       </c>
       <c r="BO44" t="inlineStr">
         <is>
-          <t>39.39682484721525</t>
+          <t>14.3018812003839</t>
         </is>
       </c>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>26.17541857990816</t>
+          <t>4.638263532314008</t>
         </is>
       </c>
       <c r="BQ44" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR44" t="inlineStr">
@@ -19865,82 +19865,82 @@
       </c>
       <c r="BS44" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="BT44" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BU44" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="BV44" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>13.97</t>
         </is>
       </c>
       <c r="BW44" t="inlineStr">
         <is>
-          <t>50.58%</t>
+          <t>47.50%</t>
         </is>
       </c>
       <c r="BX44" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>7.73%</t>
         </is>
       </c>
       <c r="BY44" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="BZ44" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="CA44" t="inlineStr">
         <is>
-          <t>餐飲95.78%、其他4.22% (2024年)</t>
+          <t>餐飲94.44%、零售5.56% (2024年)</t>
         </is>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>王座-觀光事業-上櫃</t>
+          <t>王品-觀光事業-上市</t>
         </is>
       </c>
       <c r="CC44" t="inlineStr">
         <is>
-          <t>觀光事業平上櫃</t>
+          <t>觀光事業右下上市</t>
         </is>
       </c>
       <c r="CD44" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CE44" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="CF44" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CG44" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CH44" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>51.88</t>
         </is>
       </c>
       <c r="CI44" t="inlineStr">
@@ -19957,22 +19957,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>128.343</t>
+          <t>84.492</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -20002,7 +20002,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -20017,32 +20017,32 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-05-23 00:00:00</t>
+          <t>2025-09-11 00:00:00</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2025-06-09 00:00:00</t>
+          <t>2025-09-18 00:00:00</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-02-21 00:00:00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-03-13 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>233.5</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -20067,12 +20067,12 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>-13.77</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -20097,92 +20097,92 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>食品｜下游｜餐飲連鎖</t>
+          <t>休閒娛樂｜｜旅館服務業</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>213.4</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>214.78</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>219.19</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>220.92</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>554.54</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>-106.67</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
@@ -20192,47 +20192,47 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>465563659.8182461</t>
+          <t>14678189.92362093</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>27360978.0</t>
+          <t>1108686.0</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>39383506.6</t>
+          <t>743122.4</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>37418389.3</t>
+          <t>740704.9</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>81902030.2</t>
+          <t>1573954.22</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>1965117</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>-8794209.991249312</t>
+          <t>-179395.1514142393</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>-8020093.736558624</t>
+          <t>-154322.1295942093</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>27360978.0</t>
+          <t>1108686.0</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
@@ -20242,27 +20242,27 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>228.5</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>2025/09/25</t>
+          <t>2025/08/14</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>王品</t>
+          <t>第一店</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr">
         <is>
-          <t>王品</t>
+          <t>第一店</t>
         </is>
       </c>
       <c r="BK45" t="inlineStr">
@@ -20277,62 +20277,62 @@
       </c>
       <c r="BM45" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BN45" t="inlineStr">
         <is>
-          <t>13.0908532754338</t>
+          <t>1.659807956104252</t>
         </is>
       </c>
       <c r="BO45" t="inlineStr">
         <is>
-          <t>14.3018812003839</t>
+          <t>2.798488053542324</t>
         </is>
       </c>
       <c r="BP45" t="inlineStr">
         <is>
-          <t>4.638263532314008</t>
+          <t>6.2629111171514</t>
         </is>
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR45" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS45" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BT45" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BU45" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BV45" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="BW45" t="inlineStr">
         <is>
-          <t>47.50%</t>
+          <t>80.39%</t>
         </is>
       </c>
       <c r="BX45" t="inlineStr">
         <is>
-          <t>7.73%</t>
+          <t>71.66%</t>
         </is>
       </c>
       <c r="BY45" t="inlineStr">
@@ -20342,17 +20342,17 @@
       </c>
       <c r="BZ45" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="CA45" t="inlineStr">
         <is>
-          <t>餐飲94.44%、零售5.56% (2024年)</t>
+          <t>租金收入75.80%、飯店客房13.88%、餐飲9.74%、其他0.59% (2024年)</t>
         </is>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>王品-觀光事業-上市</t>
+          <t>第一店-觀光事業-上市</t>
         </is>
       </c>
       <c r="CC45" t="inlineStr">
@@ -20362,32 +20362,32 @@
       </c>
       <c r="CD45" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CE45" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="CF45" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="CG45" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="CH45" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI45" t="inlineStr">
         <is>
-          <t>** 食品 - 餐飲連鎖</t>
+          <t>** 休閒娛樂 - 旅館服務業</t>
         </is>
       </c>
       <c r="CJ45" t="inlineStr">
@@ -20399,52 +20399,52 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>702.221</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>84.492</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -20454,37 +20454,37 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-09-11 00:00:00</t>
+          <t>2025-07-23 00:00:00</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2025-09-18 00:00:00</t>
+          <t>2025-09-16 00:00:00</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2025-02-21 00:00:00</t>
+          <t>2025-03-06 00:00:00</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -20494,12 +20494,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-18.41</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-15.09</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -20524,12 +20524,12 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -20538,448 +20538,6 @@
         </is>
       </c>
       <c r="AC46" t="inlineStr">
-        <is>
-          <t>休閒娛樂｜｜旅館服務業</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>13.14</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>13.08</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>13.25</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>554.54</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="AT46" t="inlineStr">
-        <is>
-          <t>-100.24</t>
-        </is>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV46" t="inlineStr">
-        <is>
-          <t>14678189.92362093</t>
-        </is>
-      </c>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>1108686.0</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>743122.4</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>740704.9</t>
-        </is>
-      </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1573954.22</t>
-        </is>
-      </c>
-      <c r="BA46" t="inlineStr">
-        <is>
-          <t>2417</t>
-        </is>
-      </c>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>-179395.1514142393</t>
-        </is>
-      </c>
-      <c r="BC46" t="inlineStr">
-        <is>
-          <t>-154322.1295942093</t>
-        </is>
-      </c>
-      <c r="BD46" t="inlineStr">
-        <is>
-          <t>1108686.0</t>
-        </is>
-      </c>
-      <c r="BE46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>13.45</t>
-        </is>
-      </c>
-      <c r="BG46" t="inlineStr">
-        <is>
-          <t>2025/08/14</t>
-        </is>
-      </c>
-      <c r="BH46" t="inlineStr">
-        <is>
-          <t>-2.60</t>
-        </is>
-      </c>
-      <c r="BI46" t="inlineStr">
-        <is>
-          <t>第一店</t>
-        </is>
-      </c>
-      <c r="BJ46" t="inlineStr">
-        <is>
-          <t>第一店</t>
-        </is>
-      </c>
-      <c r="BK46" t="inlineStr">
-        <is>
-          <t>觀光事業</t>
-        </is>
-      </c>
-      <c r="BL46" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM46" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="BN46" t="inlineStr">
-        <is>
-          <t>1.659807956104252</t>
-        </is>
-      </c>
-      <c r="BO46" t="inlineStr">
-        <is>
-          <t>2.798488053542324</t>
-        </is>
-      </c>
-      <c r="BP46" t="inlineStr">
-        <is>
-          <t>6.2629111171514</t>
-        </is>
-      </c>
-      <c r="BQ46" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR46" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS46" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="BT46" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="BU46" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BV46" t="inlineStr">
-        <is>
-          <t>22.59</t>
-        </is>
-      </c>
-      <c r="BW46" t="inlineStr">
-        <is>
-          <t>80.39%</t>
-        </is>
-      </c>
-      <c r="BX46" t="inlineStr">
-        <is>
-          <t>71.66%</t>
-        </is>
-      </c>
-      <c r="BY46" t="inlineStr">
-        <is>
-          <t>34.66</t>
-        </is>
-      </c>
-      <c r="BZ46" t="inlineStr">
-        <is>
-          <t>6550</t>
-        </is>
-      </c>
-      <c r="CA46" t="inlineStr">
-        <is>
-          <t>租金收入75.80%、飯店客房13.88%、餐飲9.74%、其他0.59% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB46" t="inlineStr">
-        <is>
-          <t>第一店-觀光事業-上市</t>
-        </is>
-      </c>
-      <c r="CC46" t="inlineStr">
-        <is>
-          <t>觀光事業右下上市</t>
-        </is>
-      </c>
-      <c r="CD46" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
-      </c>
-      <c r="CE46" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
-      </c>
-      <c r="CF46" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="CG46" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="CH46" t="inlineStr">
-        <is>
-          <t>19.57</t>
-        </is>
-      </c>
-      <c r="CI46" t="inlineStr">
-        <is>
-          <t>** 休閒娛樂 - 旅館服務業</t>
-        </is>
-      </c>
-      <c r="CJ46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>【d2】</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2476</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>702.221</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2025-07-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>2025-09-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>2025-03-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>95.8</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>92.1</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>-18.41</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>-15.09</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
         <is>
           <t>平面顯示器｜上游｜其他零組件
 生技醫療｜｜電子零組件、塑膠零件、五金零件
@@ -20990,169 +20548,611 @@
 連接器｜上游｜電鍍材料</t>
         </is>
       </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>57.14</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>33.86</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>-7.26</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>-2.47</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>87.06</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>88.44</t>
+        </is>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>95.36</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>97.78</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>13.63</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>-2.75</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>-138.26</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>351845462.9448373</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>60837416.0</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>60572677.2</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>59826908.2</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>204019569.06</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>745769</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>-23466461.21743436</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>-16683257.10160669</t>
+        </is>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>60837416.0</t>
+        </is>
+      </c>
+      <c r="BE46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF46" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG46" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ46" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK46" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL46" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM46" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN46" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO46" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP46" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ46" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR46" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS46" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BT46" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="BU46" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV46" t="inlineStr">
+        <is>
+          <t>22.44</t>
+        </is>
+      </c>
+      <c r="BW46" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX46" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY46" t="inlineStr">
+        <is>
+          <t>35.33</t>
+        </is>
+      </c>
+      <c r="BZ46" t="inlineStr">
+        <is>
+          <t>18411</t>
+        </is>
+      </c>
+      <c r="CA46" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB46" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC46" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD46" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="CE46" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="CF46" t="inlineStr">
+        <is>
+          <t>86.1</t>
+        </is>
+      </c>
+      <c r="CG46" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="CH46" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI46" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>價_量;【b1】;【x】看好</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2234.064</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1485.0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-18.39</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1485.0</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1485.0</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1470.0</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1425.0</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>印刷電路板｜中游｜銅箔基板</t>
+        </is>
+      </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>60.41</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>1455.0</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>1415.0</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>95.36</t>
+          <t>1316.9</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>1289.25</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>-138.26</t>
+          <t>-37.69</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>4657745816.070721</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>60837416.0</t>
+          <t>3330315145.0</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>60572677.2</t>
+          <t>4728009802.0</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>59826908.2</t>
+          <t>5793562119.5</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>204019569.06</t>
+          <t>5612861675.82</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>745769</t>
+          <t>-1065552317</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>-23466461.21743436</t>
+          <t>-129916929.6226659</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>-16683257.10160669</t>
+          <t>-410119672.9935198</t>
         </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>60837416.0</t>
+          <t>3330315145.0</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>1360.0</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/11/10</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="BK47" t="inlineStr">
@@ -21167,27 +21167,27 @@
       </c>
       <c r="BM47" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BN47" t="inlineStr">
         <is>
-          <t>-7.291353668658945</t>
+          <t>0.8301728749507388</t>
         </is>
       </c>
       <c r="BO47" t="inlineStr">
         <is>
-          <t>11.64963320584363</t>
+          <t>38.79499123379972</t>
         </is>
       </c>
       <c r="BP47" t="inlineStr">
         <is>
-          <t>10.65346457950322</t>
+          <t>49.92179810875667</t>
         </is>
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR47" t="inlineStr">
@@ -21197,32 +21197,32 @@
       </c>
       <c r="BS47" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BT47" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BU47" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>70.33</t>
         </is>
       </c>
       <c r="BV47" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="BW47" t="inlineStr">
         <is>
-          <t>29.60%</t>
+          <t>30.13%</t>
         </is>
       </c>
       <c r="BX47" t="inlineStr">
         <is>
-          <t>15.93%</t>
+          <t>19.84%</t>
         </is>
       </c>
       <c r="BY47" t="inlineStr">
@@ -21232,17 +21232,17 @@
       </c>
       <c r="BZ47" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>530939</t>
         </is>
       </c>
       <c r="CA47" t="inlineStr">
         <is>
-          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+          <t>銅箔基板(CCL)56.09%、黏合片42.56%、多層壓合板0.74%、其他0.61% (2024年)</t>
         </is>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>鉅祥-電子零組件業-上市</t>
+          <t>台光電-電子零組件業-上市</t>
         </is>
       </c>
       <c r="CC47" t="inlineStr">
@@ -21252,32 +21252,32 @@
       </c>
       <c r="CD47" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="CE47" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="CF47" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>1475.0</t>
         </is>
       </c>
       <c r="CG47" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>1485.0</t>
         </is>
       </c>
       <c r="CH47" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>124.18</t>
         </is>
       </c>
       <c r="CI47" t="inlineStr">
         <is>
-          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+          <t>** 印刷電路板 - 銅箔基板</t>
         </is>
       </c>
       <c r="CJ47" t="inlineStr">
@@ -21289,22 +21289,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>價_量;【b1】;【x】看好</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2234.064</t>
+          <t>7528.358</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -21314,7 +21314,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1485.0</t>
+          <t>588.0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -21329,97 +21329,97 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-18.39</t>
+          <t>-26.34</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>465.5</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>582.0</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>505.0</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>456.5</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>1485.0</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>1485.0</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1470.0</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1425.0</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>15.98</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -21429,172 +21429,172 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>印刷電路板｜中游｜銅箔基板</t>
+          <t>印刷電路板｜中游｜硬板、軟板、IC載板製造</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>232</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>1455.0</t>
+          <t>591.0</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>1415.0</t>
+          <t>571.42</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>1316.9</t>
+          <t>489.81</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>1289.25</t>
+          <t>479.03</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>35.79</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>-37.69</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2025/12/08</t>
+          <t>2025/10/30</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>4657745816.070721</t>
+          <t>3623603104.275106</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>3330315145.0</t>
+          <t>4464561149.0</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>4728009802.0</t>
+          <t>6552207302.6</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>5793562119.5</t>
+          <t>8894876457.7</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>5612861675.82</t>
+          <t>6107348442.0</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>-1065552317</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>-129916929.6226659</t>
+          <t>301988428.9376118</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>-410119672.9935198</t>
+          <t>-676391336.0430756</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>3330315145.0</t>
+          <t>4464561149.0</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>1360.0</t>
+          <t>567.0</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="BK48" t="inlineStr">
@@ -21609,22 +21609,22 @@
       </c>
       <c r="BM48" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN48" t="inlineStr">
         <is>
-          <t>0.8301728749507388</t>
+          <t>-6.142594752152546</t>
         </is>
       </c>
       <c r="BO48" t="inlineStr">
         <is>
-          <t>38.79499123379972</t>
+          <t>83.63472764852382</t>
         </is>
       </c>
       <c r="BP48" t="inlineStr">
         <is>
-          <t>49.92179810875667</t>
+          <t>53.14162404911895</t>
         </is>
       </c>
       <c r="BQ48" t="inlineStr">
@@ -21639,32 +21639,32 @@
       </c>
       <c r="BS48" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="BT48" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BU48" t="inlineStr">
         <is>
-          <t>70.33</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="BV48" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>36.93</t>
         </is>
       </c>
       <c r="BW48" t="inlineStr">
         <is>
-          <t>30.13%</t>
+          <t>35.56%</t>
         </is>
       </c>
       <c r="BX48" t="inlineStr">
         <is>
-          <t>19.84%</t>
+          <t>26.28%</t>
         </is>
       </c>
       <c r="BY48" t="inlineStr">
@@ -21674,17 +21674,17 @@
       </c>
       <c r="BZ48" t="inlineStr">
         <is>
-          <t>530939</t>
+          <t>289201</t>
         </is>
       </c>
       <c r="CA48" t="inlineStr">
         <is>
-          <t>銅箔基板(CCL)56.09%、黏合片42.56%、多層壓合板0.74%、其他0.61% (2024年)</t>
+          <t>印刷電路板(PCB)100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>台光電-電子零組件業-上市</t>
+          <t>金像電-電子零組件業-上市</t>
         </is>
       </c>
       <c r="CC48" t="inlineStr">
@@ -21694,32 +21694,32 @@
       </c>
       <c r="CD48" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>597.0</t>
         </is>
       </c>
       <c r="CE48" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CF48" t="inlineStr">
         <is>
-          <t>1475.0</t>
+          <t>586.0</t>
         </is>
       </c>
       <c r="CG48" t="inlineStr">
         <is>
-          <t>1485.0</t>
+          <t>588.0</t>
         </is>
       </c>
       <c r="CH48" t="inlineStr">
         <is>
-          <t>124.18</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="CI48" t="inlineStr">
         <is>
-          <t>** 印刷電路板 - 銅箔基板</t>
+          <t>** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
       <c r="CJ48" t="inlineStr">
@@ -21731,22 +21731,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7528.358</t>
+          <t>5766.443</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>588.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -21771,12 +21771,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-26.34</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -21786,227 +21786,227 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2025-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2025-09-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>61.4</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>-7.95</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>8.07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>3.89</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>5766</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2025-09-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>465.5</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>582.0</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>505.0</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>456.5</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15.98</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>-2.04</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>印刷電路板｜中游｜硬板、軟板、IC載板製造</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>7528</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>11.76</t>
-        </is>
-      </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>591.0</t>
+          <t>49.76000000000001</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>571.42</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>489.81</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>479.03</t>
+          <t>54.44</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-125.14</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2025/10/30</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>3623603104.275106</t>
+          <t>1800594666.596154</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>4464561149.0</t>
+          <t>295423176.0</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>6552207302.6</t>
+          <t>137890724.8</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>8894876457.7</t>
+          <t>120028469.2</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>6107348442.0</t>
+          <t>321841062.64</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>17862255</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>301988428.9376118</t>
+          <t>-31570347.59738759</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>-676391336.0430756</t>
+          <t>-5096801.601195753</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>4464561149.0</t>
+          <t>295423176.0</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
@@ -22016,32 +22016,32 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>567.0</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/07/16</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>矽統</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>矽統</t>
         </is>
       </c>
       <c r="BK49" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>半導體業</t>
         </is>
       </c>
       <c r="BL49" t="inlineStr">
@@ -22051,117 +22051,117 @@
       </c>
       <c r="BM49" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BN49" t="inlineStr">
         <is>
-          <t>-6.142594752152546</t>
+          <t>-13.87084244523547</t>
         </is>
       </c>
       <c r="BO49" t="inlineStr">
         <is>
-          <t>83.63472764852382</t>
+          <t>130.1377653297695</t>
         </is>
       </c>
       <c r="BP49" t="inlineStr">
         <is>
-          <t>53.14162404911895</t>
+          <t>430.6808501892076</t>
         </is>
       </c>
       <c r="BQ49" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR49" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS49" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT49" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU49" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BV49" t="inlineStr">
         <is>
-          <t>36.93</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BW49" t="inlineStr">
         <is>
-          <t>35.56%</t>
+          <t>27.13%</t>
         </is>
       </c>
       <c r="BX49" t="inlineStr">
         <is>
-          <t>26.28%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="BY49" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>145.77</t>
         </is>
       </c>
       <c r="BZ49" t="inlineStr">
         <is>
-          <t>289201</t>
+          <t>26831</t>
         </is>
       </c>
       <c r="CA49" t="inlineStr">
         <is>
-          <t>印刷電路板(PCB)100.00% (2024年)</t>
+          <t>積體電路(IC)100.00% (2024年)</t>
         </is>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>金像電-電子零組件業-上市</t>
+          <t>矽統-半導體業-上市</t>
         </is>
       </c>
       <c r="CC49" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>半導體業平上市</t>
         </is>
       </c>
       <c r="CD49" t="inlineStr">
         <is>
-          <t>597.0</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE49" t="inlineStr">
         <is>
-          <t>602.0</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF49" t="inlineStr">
         <is>
-          <t>586.0</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CG49" t="inlineStr">
         <is>
-          <t>588.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH49" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CI49" t="inlineStr">
         <is>
-          <t>** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+          <t>** 半導體 - IC設計</t>
         </is>
       </c>
       <c r="CJ49" t="inlineStr">
@@ -22178,17 +22178,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5766.443</t>
+          <t>4168.557</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -22213,12 +22213,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -22228,37 +22228,37 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2025-10-23 00:00:00</t>
+          <t>2025-11-03 00:00:00</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2025-10-29 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2025-09-18 00:00:00</t>
+          <t>2025-10-03 00:00:00</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2025-09-26 00:00:00</t>
+          <t>2025-10-07 00:00:00</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>1075.0</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>979.0</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -22268,12 +22268,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>1105.0</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>1025.0</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -22283,12 +22283,12 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -22298,12 +22298,12 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>25.40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -22313,324 +22313,324 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>通信網路｜下游｜網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>-2.25</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>993.6</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>978.05</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>1000.54</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>1006.61</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>45.19</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>-2.94</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>60.79</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>-104.84</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>4007754425.917256</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>4115348034.0</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>5443790406.8</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>5693407804.1</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>5746625068.72</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>-249617397</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>-66295259.43892292</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>-197072923.4113121</t>
+        </is>
+      </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>4115348034.0</t>
+        </is>
+      </c>
+      <c r="BE50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF50" t="inlineStr">
+        <is>
+          <t>705.0</t>
+        </is>
+      </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>2025/05/19</t>
+        </is>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>38.58</t>
+        </is>
+      </c>
+      <c r="BI50" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="BJ50" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="BK50" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BL50" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM50" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>-8.21</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>-1.74</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>49.76000000000001</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>53.49</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>54.44</t>
-        </is>
-      </c>
-      <c r="AP50" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>6.32</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr">
-        <is>
-          <t>-125.14</t>
-        </is>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV50" t="inlineStr">
-        <is>
-          <t>1800594666.596154</t>
-        </is>
-      </c>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>295423176.0</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>137890724.8</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>120028469.2</t>
-        </is>
-      </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>321841062.64</t>
-        </is>
-      </c>
-      <c r="BA50" t="inlineStr">
-        <is>
-          <t>17862255</t>
-        </is>
-      </c>
-      <c r="BB50" t="inlineStr">
-        <is>
-          <t>-31570347.59738759</t>
-        </is>
-      </c>
-      <c r="BC50" t="inlineStr">
-        <is>
-          <t>-5096801.601195753</t>
-        </is>
-      </c>
-      <c r="BD50" t="inlineStr">
-        <is>
-          <t>295423176.0</t>
-        </is>
-      </c>
-      <c r="BE50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF50" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr">
-        <is>
-          <t>2025/07/16</t>
-        </is>
-      </c>
-      <c r="BH50" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
-      <c r="BI50" t="inlineStr">
-        <is>
-          <t>矽統</t>
-        </is>
-      </c>
-      <c r="BJ50" t="inlineStr">
-        <is>
-          <t>矽統</t>
-        </is>
-      </c>
-      <c r="BK50" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="BL50" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM50" t="inlineStr">
+      <c r="BN50" t="inlineStr">
+        <is>
+          <t>-3.920801023369761</t>
+        </is>
+      </c>
+      <c r="BO50" t="inlineStr">
+        <is>
+          <t>114.6968958092869</t>
+        </is>
+      </c>
+      <c r="BP50" t="inlineStr">
+        <is>
+          <t>142.5037394584292</t>
+        </is>
+      </c>
+      <c r="BQ50" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR50" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS50" t="inlineStr">
+        <is>
+          <t>11.01</t>
+        </is>
+      </c>
+      <c r="BT50" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BN50" t="inlineStr">
-        <is>
-          <t>-13.87084244523547</t>
-        </is>
-      </c>
-      <c r="BO50" t="inlineStr">
-        <is>
-          <t>130.1377653297695</t>
-        </is>
-      </c>
-      <c r="BP50" t="inlineStr">
-        <is>
-          <t>430.6808501892076</t>
-        </is>
-      </c>
-      <c r="BQ50" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR50" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS50" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="BT50" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
       <c r="BU50" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>130.52</t>
         </is>
       </c>
       <c r="BV50" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BW50" t="inlineStr">
         <is>
-          <t>27.13%</t>
+          <t>17.16%</t>
         </is>
       </c>
       <c r="BX50" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>12.34%</t>
         </is>
       </c>
       <c r="BY50" t="inlineStr">
         <is>
-          <t>145.77</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ50" t="inlineStr">
         <is>
-          <t>26831</t>
+          <t>548211</t>
         </is>
       </c>
       <c r="CA50" t="inlineStr">
         <is>
-          <t>積體電路(IC)100.00% (2024年)</t>
+          <t>網路交換器57.00%、網路應用設備36.00%、網路接取設備4.00%、其他3.00% (2024年)</t>
         </is>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>矽統-半導體業-上市</t>
+          <t>智邦-通信網路業-上市</t>
         </is>
       </c>
       <c r="CC50" t="inlineStr">
         <is>
-          <t>半導體業平上市</t>
+          <t>通信網路業右上上市</t>
         </is>
       </c>
       <c r="CD50" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CE50" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>1005.0</t>
         </is>
       </c>
       <c r="CF50" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="CG50" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="CH50" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="CI50" t="inlineStr">
         <is>
-          <t>** 半導體 - IC設計</t>
+          <t>** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
       <c r="CJ50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4168.557</t>
+          <t>5977.776</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>977.0</t>
+          <t>979.0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -22655,82 +22655,82 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-10-07 00:00:00</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-10-07 00:00:00</t>
+          <t>2025-10-20 00:00:00</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1075.0</t>
+          <t>989.0</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>979.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989.0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1105.0</t>
+          <t>987.0</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1025.0</t>
+          <t>1015.0</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -22740,12 +22740,12 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>25.40</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -22754,448 +22754,6 @@
         </is>
       </c>
       <c r="AC51" t="inlineStr">
-        <is>
-          <t>通信網路｜下游｜網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>4169</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>14.12</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>21.11</t>
-        </is>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>-2.25</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>993.6</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>978.05</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>1000.54</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>1006.61</t>
-        </is>
-      </c>
-      <c r="AP51" t="inlineStr">
-        <is>
-          <t>45.19</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>-1.61</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>60.79</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr">
-        <is>
-          <t>-104.84</t>
-        </is>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV51" t="inlineStr">
-        <is>
-          <t>4007754425.917256</t>
-        </is>
-      </c>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>4115348034.0</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>5443790406.8</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>5693407804.1</t>
-        </is>
-      </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>5746625068.72</t>
-        </is>
-      </c>
-      <c r="BA51" t="inlineStr">
-        <is>
-          <t>-249617397</t>
-        </is>
-      </c>
-      <c r="BB51" t="inlineStr">
-        <is>
-          <t>-66295259.43892292</t>
-        </is>
-      </c>
-      <c r="BC51" t="inlineStr">
-        <is>
-          <t>-197072923.4113121</t>
-        </is>
-      </c>
-      <c r="BD51" t="inlineStr">
-        <is>
-          <t>4115348034.0</t>
-        </is>
-      </c>
-      <c r="BE51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF51" t="inlineStr">
-        <is>
-          <t>705.0</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
-        <is>
-          <t>2025/05/19</t>
-        </is>
-      </c>
-      <c r="BH51" t="inlineStr">
-        <is>
-          <t>38.58</t>
-        </is>
-      </c>
-      <c r="BI51" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="BJ51" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="BK51" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BL51" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM51" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="BN51" t="inlineStr">
-        <is>
-          <t>-3.920801023369761</t>
-        </is>
-      </c>
-      <c r="BO51" t="inlineStr">
-        <is>
-          <t>114.6968958092869</t>
-        </is>
-      </c>
-      <c r="BP51" t="inlineStr">
-        <is>
-          <t>142.5037394584292</t>
-        </is>
-      </c>
-      <c r="BQ51" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR51" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="BS51" t="inlineStr">
-        <is>
-          <t>11.01</t>
-        </is>
-      </c>
-      <c r="BT51" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="BU51" t="inlineStr">
-        <is>
-          <t>130.52</t>
-        </is>
-      </c>
-      <c r="BV51" t="inlineStr">
-        <is>
-          <t>24.26</t>
-        </is>
-      </c>
-      <c r="BW51" t="inlineStr">
-        <is>
-          <t>17.16%</t>
-        </is>
-      </c>
-      <c r="BX51" t="inlineStr">
-        <is>
-          <t>12.34%</t>
-        </is>
-      </c>
-      <c r="BY51" t="inlineStr">
-        <is>
-          <t>29.89</t>
-        </is>
-      </c>
-      <c r="BZ51" t="inlineStr">
-        <is>
-          <t>548211</t>
-        </is>
-      </c>
-      <c r="CA51" t="inlineStr">
-        <is>
-          <t>網路交換器57.00%、網路應用設備36.00%、網路接取設備4.00%、其他3.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB51" t="inlineStr">
-        <is>
-          <t>智邦-通信網路業-上市</t>
-        </is>
-      </c>
-      <c r="CC51" t="inlineStr">
-        <is>
-          <t>通信網路業右上上市</t>
-        </is>
-      </c>
-      <c r="CD51" t="inlineStr">
-        <is>
-          <t>994.0</t>
-        </is>
-      </c>
-      <c r="CE51" t="inlineStr">
-        <is>
-          <t>1005.0</t>
-        </is>
-      </c>
-      <c r="CF51" t="inlineStr">
-        <is>
-          <t>977.0</t>
-        </is>
-      </c>
-      <c r="CG51" t="inlineStr">
-        <is>
-          <t>977.0</t>
-        </is>
-      </c>
-      <c r="CH51" t="inlineStr">
-        <is>
-          <t>88.73</t>
-        </is>
-      </c>
-      <c r="CI51" t="inlineStr">
-        <is>
-          <t>** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
-        </is>
-      </c>
-      <c r="CJ51" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>【d1】;【x】看好</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>5977.776</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>979.0</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>989.0</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>989.0</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>987.0</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>1015.0</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>-2.56</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
         <is>
           <t>休閒娛樂｜｜休閒車業
 其他｜｜特殊照明業
@@ -23258,297 +22816,297 @@
 電腦週邊｜下游｜精簡型電腦</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>395</t>
         </is>
       </c>
-      <c r="AE52" t="inlineStr">
+      <c r="AE51" t="inlineStr">
         <is>
           <t>5978</t>
         </is>
       </c>
-      <c r="AF52" t="inlineStr">
+      <c r="AF51" t="inlineStr">
         <is>
           <t>70.15</t>
         </is>
       </c>
-      <c r="AG52" t="inlineStr">
+      <c r="AG51" t="inlineStr">
         <is>
           <t>82.56</t>
         </is>
       </c>
-      <c r="AH52" t="inlineStr">
+      <c r="AH51" t="inlineStr">
         <is>
           <t>-0.97</t>
         </is>
       </c>
-      <c r="AI52" t="inlineStr">
+      <c r="AI51" t="inlineStr">
         <is>
           <t>4.54</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
+      <c r="AJ51" t="inlineStr">
         <is>
           <t>-2.0</t>
         </is>
       </c>
-      <c r="AK52" t="inlineStr">
+      <c r="AK51" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
+      <c r="AL51" t="inlineStr">
         <is>
           <t>988.6</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
+      <c r="AM51" t="inlineStr">
         <is>
           <t>945.7</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
+      <c r="AN51" t="inlineStr">
         <is>
           <t>965.02</t>
         </is>
       </c>
-      <c r="AO52" t="inlineStr">
+      <c r="AO51" t="inlineStr">
         <is>
           <t>883.09</t>
         </is>
       </c>
-      <c r="AP52" t="inlineStr">
+      <c r="AP51" t="inlineStr">
         <is>
           <t>371.35</t>
         </is>
       </c>
-      <c r="AQ52" t="inlineStr">
+      <c r="AQ51" t="inlineStr">
         <is>
           <t>8.18</t>
         </is>
       </c>
-      <c r="AR52" t="inlineStr">
+      <c r="AR51" t="inlineStr">
         <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="AS52" t="inlineStr">
+      <c r="AS51" t="inlineStr">
         <is>
           <t>64.81</t>
         </is>
       </c>
-      <c r="AT52" t="inlineStr">
+      <c r="AT51" t="inlineStr">
         <is>
           <t>-97.32</t>
         </is>
       </c>
-      <c r="AU52" t="inlineStr">
+      <c r="AU51" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="AV52" t="inlineStr">
+      <c r="AV51" t="inlineStr">
         <is>
           <t>6568820410.391796</t>
         </is>
       </c>
-      <c r="AW52" t="inlineStr">
+      <c r="AW51" t="inlineStr">
         <is>
           <t>5848094798.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>11072370366.0</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr">
+      <c r="AY51" t="inlineStr">
         <is>
           <t>10867779649.8</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>13591929529.98</t>
         </is>
       </c>
-      <c r="BA52" t="inlineStr">
+      <c r="BA51" t="inlineStr">
         <is>
           <t>204590716</t>
         </is>
       </c>
-      <c r="BB52" t="inlineStr">
+      <c r="BB51" t="inlineStr">
         <is>
           <t>-313050744.4381415</t>
         </is>
       </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BC51" t="inlineStr">
         <is>
           <t>-863095738.4523869</t>
         </is>
       </c>
-      <c r="BD52" t="inlineStr">
+      <c r="BD51" t="inlineStr">
         <is>
           <t>5848094798.0</t>
         </is>
       </c>
-      <c r="BE52" t="inlineStr">
+      <c r="BE51" t="inlineStr">
         <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="BF52" t="inlineStr">
+      <c r="BF51" t="inlineStr">
         <is>
           <t>378.0</t>
         </is>
       </c>
-      <c r="BG52" t="inlineStr">
+      <c r="BG51" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
       </c>
-      <c r="BH52" t="inlineStr">
+      <c r="BH51" t="inlineStr">
         <is>
           <t>158.99</t>
         </is>
       </c>
-      <c r="BI52" t="inlineStr">
+      <c r="BI51" t="inlineStr">
         <is>
           <t>台達電</t>
         </is>
       </c>
-      <c r="BJ52" t="inlineStr">
+      <c r="BJ51" t="inlineStr">
         <is>
           <t>台達電</t>
         </is>
       </c>
-      <c r="BK52" t="inlineStr">
+      <c r="BK51" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BL52" t="inlineStr">
+      <c r="BL51" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM52" t="inlineStr">
+      <c r="BM51" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="BN52" t="inlineStr">
+      <c r="BN51" t="inlineStr">
         <is>
           <t>0.5656582232900037</t>
         </is>
       </c>
-      <c r="BO52" t="inlineStr">
+      <c r="BO51" t="inlineStr">
         <is>
           <t>47.83155119056676</t>
         </is>
       </c>
-      <c r="BP52" t="inlineStr">
+      <c r="BP51" t="inlineStr">
         <is>
           <t>30.3369714889051</t>
         </is>
       </c>
-      <c r="BQ52" t="inlineStr">
+      <c r="BQ51" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BR52" t="inlineStr">
+      <c r="BR51" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="BS52" t="inlineStr">
+      <c r="BS51" t="inlineStr">
         <is>
           <t>10.56</t>
         </is>
       </c>
-      <c r="BT52" t="inlineStr">
+      <c r="BT51" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="BU52" t="inlineStr">
+      <c r="BU51" t="inlineStr">
         <is>
           <t>57.87</t>
         </is>
       </c>
-      <c r="BV52" t="inlineStr">
+      <c r="BV51" t="inlineStr">
         <is>
           <t>50.91</t>
         </is>
       </c>
-      <c r="BW52" t="inlineStr">
+      <c r="BW51" t="inlineStr">
         <is>
           <t>34.87%</t>
         </is>
       </c>
-      <c r="BX52" t="inlineStr">
+      <c r="BX51" t="inlineStr">
         <is>
           <t>16.50%</t>
         </is>
       </c>
-      <c r="BY52" t="inlineStr">
+      <c r="BY51" t="inlineStr">
         <is>
           <t>35.33</t>
         </is>
       </c>
-      <c r="BZ52" t="inlineStr">
+      <c r="BZ51" t="inlineStr">
         <is>
           <t>2542995</t>
         </is>
       </c>
-      <c r="CA52" t="inlineStr">
+      <c r="CA51" t="inlineStr">
         <is>
           <t>電源及零組件53.00%、基礎設施24.00%、自動化業務12.00%、交通業11.00% (2024年)</t>
         </is>
       </c>
-      <c r="CB52" t="inlineStr">
+      <c r="CB51" t="inlineStr">
         <is>
           <t>台達電-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CC52" t="inlineStr">
+      <c r="CC51" t="inlineStr">
         <is>
           <t>電子零組件業右上上市</t>
         </is>
       </c>
-      <c r="CD52" t="inlineStr">
+      <c r="CD51" t="inlineStr">
         <is>
           <t>985.0</t>
         </is>
       </c>
-      <c r="CE52" t="inlineStr">
+      <c r="CE51" t="inlineStr">
         <is>
           <t>993.0</t>
         </is>
       </c>
-      <c r="CF52" t="inlineStr">
+      <c r="CF51" t="inlineStr">
         <is>
           <t>970.0</t>
         </is>
       </c>
-      <c r="CG52" t="inlineStr">
+      <c r="CG51" t="inlineStr">
         <is>
           <t>979.0</t>
         </is>
       </c>
-      <c r="CH52" t="inlineStr">
+      <c r="CH51" t="inlineStr">
         <is>
           <t>92.68</t>
         </is>
       </c>
-      <c r="CI52" t="inlineStr">
+      <c r="CI51" t="inlineStr">
         <is>
           <t>** 休閒娛樂 - 休閒車業** 半導體 - 生產製程及檢測設備、IC模組、IC通路、LED驅動IC、消費性IC、微控制器IC、電源管理IC** 電腦及週邊設備 - 電源供應器、散熱片、風扇馬達、散熱模組、筆記型電腦、桌上型電腦、精簡型電腦、安全監控系統** 平面顯示器 - 其他零組件** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、光通訊設備(如光纖電纜、光傳輸設備)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 被動元件 - 電阻器、電容器、電感器** 電機機械 - 傳動元件、電控元件、專用機械(如紡織成衣生產用機械、食品飲料生產用機械、農林用機械等)、輸送機械及零配件** 軟體服務 - 應用/系統軟體設計開發** 建材營造 - 機電工程** 其他 - 特殊照明業** 汽車 - 其他** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備、機器學習、電腦視覺、運算設備** 雲端運算 - 電力設備、冷卻設備、設備管理軟體、系統整合、顧問諮詢、設備安裝服務、伺服器、SaaS** 大數據 - 系統整合、顧問諮詢、領域解決方案、運算元件與設備** 太空衛星科技 - 天線/射頻基頻** 體驗科技 - 電池模組** LED照明產業 - 燈具/應用** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件、電動汽車、電動機車、電動自行車** 太陽能產業 - 太陽能發電設備/系統及系統工程、太陽能電廠** 風力發電 - 監控系統、電力系統** 能源元件 - 電池芯、電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施、能源管理服務、系統整合服務** 醫療器材 - 塑化材料、生物檢測、其他、醫療器材代理</t>
         </is>
       </c>
-      <c r="CJ52" t="inlineStr">
+      <c r="CJ51" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checkGreat.xlsx
+++ b/Result/checkGreat.xlsx
@@ -998,12 +998,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-02-06 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>118287.1835443038</t>
+          <t>70324.97076023392</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>-30626.34535433344</t>
+          <t>-30626.34535433455</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-28853.48345372784</t>
+          <t>-28853.4834537281</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>3.147699757869249</t>
+          <t>13.86382813007075</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>-20.89914945321993</t>
+          <t>32.09758791195</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.572287641121728</t>
+          <t>32.09758791195</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>52.59</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-12-05 00:00:00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-12-13 00:00:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-01-30 00:00:00</t>
+          <t>2025-09-11 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-132.07</t>
+          <t>-109.65</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>20568.78481012658</t>
+          <t>50150.29824561403</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2564.558961188781</t>
+          <t>2564.558961187478</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>7289.045912996105</t>
+          <t>7289.045912995825</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1924,17 +1924,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>29.43879282087261</t>
+          <t>-38.21297139599115</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.60055120831598</t>
+          <t>19.09002683107838</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>27.4554949257371</t>
+          <t>19.09002683107838</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-09 00:00:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-12 00:00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-09-15 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-109.13</t>
+          <t>-107.28</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>34623.79113924051</t>
+          <t>60151.52357563851</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-1887.668728227526</t>
+          <t>-1887.668728227026</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-1630.541628297102</t>
+          <t>-1630.541628296995</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2456,17 +2456,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>111.490726435334</t>
+          <t>-77.25926567071166</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>1106.223324730428</t>
+          <t>476.8160741885626</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1760.021493820526</t>
+          <t>476.8160741885626</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-130.53</t>
+          <t>-120.77</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>2345603540.234177</t>
+          <t>2376346251.406433</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
@@ -2928,12 +2928,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-217253314.9614288</t>
+          <t>-217253314.961409</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-213128712.1573791</t>
+          <t>-213128712.1573748</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2988,17 +2988,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-2.399499201060057</t>
+          <t>4.854339856199135</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>13.34315827586402</t>
+          <t>16.68333000066653</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>26.9731420171207</t>
+          <t>16.68333000066653</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>33.43%</t>
+          <t>33.42%</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>20.86%</t>
+          <t>21.49%</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3260,22 +3260,22 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/17</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/27</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2026-02-11 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>3653881091.550632</t>
+          <t>1740067689.80117</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-535341824.5136742</t>
+          <t>-535341824.513673</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3520,17 +3520,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>6.501427014329555</t>
+          <t>-2.765196458111179</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>44.2857363981116</t>
+          <t>59.1662920401225</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.54054518102996</t>
+          <t>59.1662920401225</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-02-15 00:00:00</t>
+          <t>2026-02-21 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>8.375331754230759</t>
+          <t>4.232168907567451</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>62.81715985971652</t>
+          <t>80.56949437074613</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>62.42417783616822</t>
+          <t>80.56949437074613</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-02-15 00:00:00</t>
+          <t>2026-02-21 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>258125.1772151898</t>
+          <t>263803.550209205</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>125425.342555576</t>
+          <t>125425.3425555268</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>151915.6932864152</t>
+          <t>151915.6932864046</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4585,17 +4585,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.72035989877847</t>
+          <t>50.44414016737436</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>2.463909575758883</t>
+          <t>142.0008905569161</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>27.22396910380253</t>
+          <t>142.0008905569161</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-05 00:00:00</t>
+          <t>2025-08-06 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>82.12</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-200.31</t>
+          <t>-130.20</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>248664913.4050633</t>
+          <t>278291836.7275862</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>5856764.418776231</t>
+          <t>5856764.418786909</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-2610085.531448081</t>
+          <t>-2610085.531445786</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-5.180395006275183</t>
+          <t>0.2622130390379763</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>16.28751362990494</t>
+          <t>15.44529327399726</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.03182973316392</t>
+          <t>15.44529327399726</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2025-09-12 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-147.14</t>
+          <t>-147.09</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>2376.164556962025</t>
+          <t>3775.065789473684</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>24.16218418196721</t>
+          <t>24.16218418197378</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>286.6945559064143</t>
+          <t>286.6945559064161</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -5652,17 +5652,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>4.929592763326541</t>
+          <t>-1.045518349364615</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>13.99528927531306</t>
+          <t>1.434192264105296</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>14.46100652801929</t>
+          <t>1.434192264105296</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5844,32 +5844,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-11 00:00:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-25 00:00:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-04-01 00:00:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>2025-10-23 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-60.01</t>
+          <t>-79.48</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>2584123.563291139</t>
+          <t>4231912.334558824</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>40411.60306664033</t>
+          <t>40411.60306678298</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-58852.3904355485</t>
+          <t>-58852.390435518</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -6184,17 +6184,17 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>4.481221521735546</t>
+          <t>5.534746698932085</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>13.8474806700645</t>
+          <t>26.94970384245431</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-2.175646583710624</t>
+          <t>26.94970384245431</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>77.63</t>
+          <t>77.63000000000001</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-42.27</t>
+          <t>-67.17</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>5500160.20886076</t>
+          <t>6176719.877777778</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>-61536.44969822086</t>
+          <t>-61536.44969778304</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>-800957.0055002831</t>
+          <t>-800957.0055001881</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6716,17 +6716,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-1.477640499870072</t>
+          <t>-11.34262867007949</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.42032861417086</t>
+          <t>21.49839809414277</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.8852195069591</t>
+          <t>21.49839809414277</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>-146.27</t>
+          <t>-122.02</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="BK13" t="inlineStr">
         <is>
-          <t>59698.74050632911</t>
+          <t>58264.59064327485</t>
         </is>
       </c>
       <c r="BL13" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>42.05045897682515</t>
+          <t>42.05045897559836</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2121.524995664437</t>
+          <t>2121.524995664175</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -7248,17 +7248,17 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>-19.76799512770736</t>
+          <t>122.6376154950125</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>-38.42361653800366</t>
+          <t>48.67018327551521</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>13.6695236803724</t>
+          <t>48.67018327551521</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>-103.44</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="BK14" t="inlineStr">
         <is>
-          <t>115739.0696202532</t>
+          <t>112238.0945945946</t>
         </is>
       </c>
       <c r="BL14" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>-1.137025918107852</t>
+          <t>-1.137025915126273</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>530.2182921622734</t>
+          <t>530.2182921629101</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -7783,17 +7783,17 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>15.01518766155281</t>
+          <t>6.151405900689569</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>20.09567116346345</t>
+          <t>43.32837327948132</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>21.71044236790081</t>
+          <t>43.32837327948132</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-30.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/12/30</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>189.5</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/11</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>-116.91</t>
+          <t>-113.52</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>115913.7278481013</t>
+          <t>112382.418128655</t>
         </is>
       </c>
       <c r="BL15" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>-2057.64023559072</t>
+          <t>-2057.640235590873</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>-4244.02353720957</t>
+          <t>-4244.023537209599</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>32.63479277640639</t>
+          <t>-60.6461029102058</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>45.02102392181374</t>
+          <t>41.28569419046279</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>105.6167012272637</t>
+          <t>41.28569419046279</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>半導體業右下上櫃</t>
+          <t>半導體業平上櫃</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-14 00:00:00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-27 00:00:00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>245.0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-01-16 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>-123.37</t>
+          <t>-118.97</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="BK16" t="inlineStr">
         <is>
-          <t>2055.197872340425</t>
+          <t>2937.865795724466</t>
         </is>
       </c>
       <c r="BL16" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>-71.72467694707807</t>
+          <t>-71.72467694705652</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>-78.32072664336488</t>
+          <t>-78.32072664336022</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -8847,17 +8847,17 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>0.187364791305526</t>
+          <t>0.0596953670798705</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>10.79179067460317</t>
+          <t>15.1915384821884</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>22.91127315273135</t>
+          <t>15.1915384821884</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-02-15 00:00:00</t>
+          <t>2026-02-21 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>2026-02-03 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-49.25</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>184363370.5696203</t>
+          <t>256801117.9035088</t>
         </is>
       </c>
       <c r="BL17" t="inlineStr">
@@ -9319,12 +9319,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>114275159.6406137</t>
+          <t>114275159.6406179</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>176279027.5003492</t>
+          <t>176279027.5003502</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -9379,17 +9379,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>3.060672768701966</t>
+          <t>-5.354031215454086</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>22.11576412444729</t>
+          <t>25.49470206079276</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>10.77852958479541</t>
+          <t>25.49470206079276</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>786.0</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/07</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>526.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>4025566519.138889</t>
+          <t>2975771934.030488</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>10187989.86018615</t>
+          <t>10187989.86008374</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>-167757068.1046429</t>
+          <t>-167757068.1046653</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -9906,22 +9906,22 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>-19.95025261291747</t>
+          <t>18.26229817419964</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.34496248647659</t>
+          <t>115.7648840982277</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>51.61700064364919</t>
+          <t>115.7648840982277</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-02-15 00:00:00</t>
+          <t>2026-02-21 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/05/15</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>261.5</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/01</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>2026-01-28 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="BK19" t="inlineStr">
         <is>
-          <t>587340.753164557</t>
+          <t>441302.4433427762</t>
         </is>
       </c>
       <c r="BL19" t="inlineStr">
@@ -10400,12 +10400,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>4624.325919379853</t>
+          <t>4624.325919375975</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>-72228.96030906565</t>
+          <t>-72228.96030906658</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -10460,17 +10460,17 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>3.510482118738622</t>
+          <t>3.307463634919555</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>102.5137867647059</t>
+          <t>98.901170919259</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>96.69448323681358</t>
+          <t>98.901170919259</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/10/23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2045.0</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/11</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2225.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-01-09 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="BK20" t="inlineStr">
         <is>
-          <t>8889587854.652777</t>
+          <t>8065945061.009146</t>
         </is>
       </c>
       <c r="BL20" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>-372941384.418655</t>
+          <t>-372941384.4185039</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>-443045469.8881664</t>
+          <t>-443045469.888135</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10954,17 +10954,17 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2150.0</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/05/08</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
@@ -10994,17 +10994,17 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>7.643355294276428</t>
+          <t>-20.19881065431387</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>143.8580378627834</t>
+          <t>121.8962600405542</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>163.6768178310121</t>
+          <t>121.8962600405542</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -11421,12 +11421,12 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>-51.41</t>
+          <t>-55.72</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>484273.2784810127</t>
+          <t>586702.418128655</t>
         </is>
       </c>
       <c r="BL21" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>-28028.56525623871</t>
+          <t>-28028.56525624707</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>-59464.02065674221</t>
+          <t>-59464.02065674408</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -11526,17 +11526,17 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>49.39023230151633</t>
+          <t>-26.5495854612142</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>35.65526862493575</t>
+          <t>56.66109820858629</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>10.1894525443122</t>
+          <t>56.66109820858629</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>-139.78</t>
+          <t>-140.52</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>22988.17088607595</t>
+          <t>37468.06666666667</t>
         </is>
       </c>
       <c r="BL22" t="inlineStr">
@@ -11999,12 +11999,12 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>-56.69943366206223</t>
+          <t>-56.69943366189632</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>587.1777100018116</t>
+          <t>587.177710001848</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -12059,17 +12059,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>35.27595522964106</t>
+          <t>-7.503566333808845</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>30.49143708116158</t>
+          <t>36.16127677446451</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>13.00297140027238</t>
+          <t>36.16127677446451</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -12191,7 +12191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-03 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="BK23" t="inlineStr">
         <is>
-          <t>166681.3481012658</t>
+          <t>106319.201754386</t>
         </is>
       </c>
       <c r="BL23" t="inlineStr">
@@ -12531,12 +12531,12 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>3373.104127409665</t>
+          <t>3373.104127408323</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2402.095965495122</t>
+          <t>2402.095965494831</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -12591,17 +12591,17 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>-44.55066921606119</t>
+          <t>79.69011494252874</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>-31.42003102652389</t>
+          <t>-8.691914118169286</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>78.67318039150594</t>
+          <t>-8.691914118169286</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -12783,32 +12783,32 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-25 00:00:00</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-31 00:00:00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-06 00:00:00</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -12818,12 +12818,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177.5</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -12833,12 +12833,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-21.74</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-10.42</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-08-11 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>-151.55</t>
+          <t>-108.91</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>11195.90506329114</t>
+          <t>18997.70175438597</t>
         </is>
       </c>
       <c r="BL24" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>10.51296958536456</t>
+          <t>10.51296958540646</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>-104.4730236547798</t>
+          <t>-104.4730236547716</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -13123,17 +13123,17 @@
       </c>
       <c r="CC24" t="inlineStr">
         <is>
-          <t>-23.28471570527719</t>
+          <t>2.758660112038413</t>
         </is>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>16.91193178021038</t>
+          <t>-26.2806948476945</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>-5.918478282753039</t>
+          <t>-26.2806948476945</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>99.12599999999999</t>
+          <t>99.126</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>11.55</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>-134.46</t>
+          <t>-113.62</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="BK25" t="inlineStr">
         <is>
-          <t>63155.68987341772</t>
+          <t>39435.78235294118</t>
         </is>
       </c>
       <c r="BL25" t="inlineStr">
@@ -13595,12 +13595,12 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>-5265.120946098223</t>
+          <t>-5265.120946099207</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>-7377.549500694495</t>
+          <t>-7377.549500694691</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
@@ -13655,17 +13655,17 @@
       </c>
       <c r="CC25" t="inlineStr">
         <is>
-          <t>4.854055052651026</t>
+          <t>15.82610227723208</t>
         </is>
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>429.084129573526</t>
+          <t>564.2920298092712</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>178.2046008290352</t>
+          <t>564.2920298092712</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>其他右下上櫃</t>
+          <t>其他右上上櫃</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
@@ -13787,7 +13787,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13827,477 +13827,477 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-0.307896187792775</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-02-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>15.95</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025/09/04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-0.307896187792775</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2025-12-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2026-02-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>12.65</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>2025/08/14</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>11.55</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
         <is>
           <t>15.95</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>12.9</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025/09/04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>12.85</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>20.70</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>12.65</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>2025/08/14</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>11.55</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>15.95</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>金融｜｜證券業</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>8019</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>68.42</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>64.47</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>11.13</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>16.33</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>16.16</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>14.54</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>13.87</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>13.464</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>-17.00</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>-20.68</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>2025/12/26</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>56057.45321637427</t>
+        </is>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>131191.0</t>
+        </is>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>127534.8</t>
+        </is>
+      </c>
+      <c r="BN26" t="inlineStr">
+        <is>
+          <t>184271.2</t>
+        </is>
+      </c>
+      <c r="BO26" t="inlineStr">
+        <is>
+          <t>99468.24</t>
+        </is>
+      </c>
+      <c r="BP26" t="inlineStr">
+        <is>
+          <t>-56736</t>
+        </is>
+      </c>
+      <c r="BQ26" t="inlineStr">
+        <is>
+          <t>4393.64736242373</t>
+        </is>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>-7892.046400155697</t>
+        </is>
+      </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>131191.0</t>
+        </is>
+      </c>
+      <c r="BT26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU26" t="inlineStr">
+        <is>
+          <t>12.85</t>
+        </is>
+      </c>
+      <c r="BV26" t="inlineStr">
         <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>12.85</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>20.70</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
+      <c r="BW26" t="inlineStr">
+        <is>
+          <t>27.63</t>
+        </is>
+      </c>
+      <c r="BX26" t="inlineStr">
+        <is>
+          <t>康和證</t>
+        </is>
+      </c>
+      <c r="BY26" t="inlineStr">
+        <is>
+          <t>康和證</t>
+        </is>
+      </c>
+      <c r="BZ26" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="CA26" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="CC26" t="inlineStr">
+        <is>
+          <t>118.8819084721092</t>
+        </is>
+      </c>
+      <c r="CD26" t="inlineStr">
+        <is>
+          <t>151.8460215459828</t>
+        </is>
+      </c>
+      <c r="CE26" t="inlineStr">
+        <is>
+          <t>151.8460215459828</t>
+        </is>
+      </c>
+      <c r="CF26" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CG26" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="CH26" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="CI26" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="CJ26" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="CK26" t="inlineStr">
+        <is>
+          <t>11.97</t>
+        </is>
+      </c>
+      <c r="CL26" t="inlineStr">
+        <is>
+          <t>89.09%</t>
+        </is>
+      </c>
+      <c r="CM26" t="inlineStr">
+        <is>
+          <t>52.81%</t>
+        </is>
+      </c>
+      <c r="CN26" t="inlineStr">
+        <is>
+          <t>30.09</t>
+        </is>
+      </c>
+      <c r="CO26" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="CP26" t="inlineStr">
+        <is>
+          <t>經紀手續費46.56%、營業證券出售損益42.58%、利息收入11.23%、股利收入4.71%、其他營業收入3.66%、營業證券透過損益按公允價值3.66%、借券1.08%、股務代理0.78%、借券及附賣回債券融券透過損0.63%、承銷業務0.46%、預期信用減損損失及迴轉利益0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>康和證-金融業-上櫃</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>金融業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr">
+        <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="CU26" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="CV26" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="CW26" t="inlineStr">
+        <is>
+          <t>15.52</t>
+        </is>
+      </c>
+      <c r="CX26" t="inlineStr">
+        <is>
+          <t>** 金融 - 證券業</t>
+        </is>
+      </c>
+      <c r="CY26" t="inlineStr">
         <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>金融｜｜證券業</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>8019</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>68.42</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr">
-        <is>
-          <t>64.47</t>
-        </is>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="AV26" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>11.13</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>16.33</t>
-        </is>
-      </c>
-      <c r="BA26" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
-      </c>
-      <c r="BB26" t="inlineStr">
-        <is>
-          <t>14.54</t>
-        </is>
-      </c>
-      <c r="BC26" t="inlineStr">
-        <is>
-          <t>13.87</t>
-        </is>
-      </c>
-      <c r="BD26" t="inlineStr">
-        <is>
-          <t>13.464</t>
-        </is>
-      </c>
-      <c r="BE26" t="inlineStr">
-        <is>
-          <t>-17.00</t>
-        </is>
-      </c>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BI26" t="inlineStr">
-        <is>
-          <t>-20.68</t>
-        </is>
-      </c>
-      <c r="BJ26" t="inlineStr">
-        <is>
-          <t>2025/12/26</t>
-        </is>
-      </c>
-      <c r="BK26" t="inlineStr">
-        <is>
-          <t>50138.10759493671</t>
-        </is>
-      </c>
-      <c r="BL26" t="inlineStr">
-        <is>
-          <t>131191.0</t>
-        </is>
-      </c>
-      <c r="BM26" t="inlineStr">
-        <is>
-          <t>127534.8</t>
-        </is>
-      </c>
-      <c r="BN26" t="inlineStr">
-        <is>
-          <t>184271.2</t>
-        </is>
-      </c>
-      <c r="BO26" t="inlineStr">
-        <is>
-          <t>99468.24</t>
-        </is>
-      </c>
-      <c r="BP26" t="inlineStr">
-        <is>
-          <t>-56736</t>
-        </is>
-      </c>
-      <c r="BQ26" t="inlineStr">
-        <is>
-          <t>4393.647362424173</t>
-        </is>
-      </c>
-      <c r="BR26" t="inlineStr">
-        <is>
-          <t>-7892.046400155552</t>
-        </is>
-      </c>
-      <c r="BS26" t="inlineStr">
-        <is>
-          <t>131191.0</t>
-        </is>
-      </c>
-      <c r="BT26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU26" t="inlineStr">
-        <is>
-          <t>12.85</t>
-        </is>
-      </c>
-      <c r="BV26" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="BW26" t="inlineStr">
-        <is>
-          <t>27.63</t>
-        </is>
-      </c>
-      <c r="BX26" t="inlineStr">
-        <is>
-          <t>康和證</t>
-        </is>
-      </c>
-      <c r="BY26" t="inlineStr">
-        <is>
-          <t>康和證</t>
-        </is>
-      </c>
-      <c r="BZ26" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="CA26" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="CC26" t="inlineStr">
-        <is>
-          <t>38.90868365106817</t>
-        </is>
-      </c>
-      <c r="CD26" t="inlineStr">
-        <is>
-          <t>50.11929403636928</t>
-        </is>
-      </c>
-      <c r="CE26" t="inlineStr">
-        <is>
-          <t>3.309474947933568</t>
-        </is>
-      </c>
-      <c r="CF26" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CG26" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="CH26" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="CI26" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="CJ26" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
-      <c r="CK26" t="inlineStr">
-        <is>
-          <t>11.97</t>
-        </is>
-      </c>
-      <c r="CL26" t="inlineStr">
-        <is>
-          <t>89.09%</t>
-        </is>
-      </c>
-      <c r="CM26" t="inlineStr">
-        <is>
-          <t>52.81%</t>
-        </is>
-      </c>
-      <c r="CN26" t="inlineStr">
-        <is>
-          <t>30.09</t>
-        </is>
-      </c>
-      <c r="CO26" t="inlineStr">
-        <is>
-          <t>11260</t>
-        </is>
-      </c>
-      <c r="CP26" t="inlineStr">
-        <is>
-          <t>經紀手續費46.56%、營業證券出售損益42.58%、利息收入11.23%、股利收入4.71%、其他營業收入3.66%、營業證券透過損益按公允價值3.66%、借券1.08%、股務代理0.78%、借券及附賣回債券融券透過損0.63%、承銷業務0.46%、預期信用減損損失及迴轉利益0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CQ26" t="inlineStr">
-        <is>
-          <t>康和證-金融業-上櫃</t>
-        </is>
-      </c>
-      <c r="CR26" t="inlineStr">
-        <is>
-          <t>金融業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="CT26" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
-      <c r="CU26" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="CV26" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
-      <c r="CW26" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
-      </c>
-      <c r="CX26" t="inlineStr">
-        <is>
-          <t>** 金融 - 證券業</t>
-        </is>
-      </c>
-      <c r="CY26" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
       <c r="CZ26" t="inlineStr">
@@ -14374,37 +14374,37 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-15 00:00:00</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-03 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-01-21 00:00:00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-27 00:00:00</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -14414,12 +14414,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -14429,12 +14429,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-37.60</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>98.46</t>
+          <t>98.46000000000001</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>99.222</t>
+          <t>99.22200000000001</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -14614,12 +14614,12 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>-105.86</t>
+          <t>-105.45</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="BK27" t="inlineStr">
         <is>
-          <t>20818.53164556962</t>
+          <t>20139.99707602339</t>
         </is>
       </c>
       <c r="BL27" t="inlineStr">
@@ -14659,12 +14659,12 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>-280.4544118250262</t>
+          <t>-280.4544118228381</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>-508.885888014468</t>
+          <t>-508.8858880139987</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="CC27" t="inlineStr">
         <is>
-          <t>5.431747844913464</t>
+          <t>-5.142586461467136</t>
         </is>
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>16.0847056070666</t>
+          <t>11.73762706833865</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>4.252926015189662</t>
+          <t>11.73762706833865</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-10-08 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="BK28" t="inlineStr">
         <is>
-          <t>1785888.816455696</t>
+          <t>965054.7953216375</t>
         </is>
       </c>
       <c r="BL28" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>90039.4654463207</t>
+          <t>90039.4654463361</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>30279.62277978286</t>
+          <t>30279.62277978659</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
@@ -15251,17 +15251,17 @@
       </c>
       <c r="CC28" t="inlineStr">
         <is>
-          <t>13.60145106872214</t>
+          <t>83.73915494169549</t>
         </is>
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>151.5626647575601</t>
+          <t>307.1096620771993</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>59.95776860488566</t>
+          <t>307.1096620771993</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
@@ -15682,12 +15682,12 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>-124.30</t>
+          <t>-124.21</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="BK29" t="inlineStr">
         <is>
-          <t>811443049.0189873</t>
+          <t>549737132.745614</t>
         </is>
       </c>
       <c r="BL29" t="inlineStr">
@@ -15727,12 +15727,12 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>-19367339.49049051</t>
+          <t>-19367339.49049809</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>-24408827.57121262</t>
+          <t>-24408827.57121426</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
@@ -15787,17 +15787,17 @@
       </c>
       <c r="CC29" t="inlineStr">
         <is>
-          <t>-11.61675528963061</t>
+          <t>2.522097247868761</t>
         </is>
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>65.94425631674915</t>
+          <t>38.47950871809501</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>56.83986344702308</t>
+          <t>38.47950871809501</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -16214,12 +16214,12 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>118.41</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>-84.21</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="BK30" t="inlineStr">
         <is>
-          <t>2010746562.879747</t>
+          <t>2619934302.98538</t>
         </is>
       </c>
       <c r="BL30" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>-101770307.9914007</t>
+          <t>-101770307.9914492</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>-200753984.7942731</t>
+          <t>-200753984.7942836</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="CC30" t="inlineStr">
         <is>
-          <t>-3.630422286391457</t>
+          <t>17.7758264363423</t>
         </is>
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>79.69397553627361</t>
+          <t>58.31377850928756</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>65.99981611348298</t>
+          <t>58.31377850928756</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2025-11-14 00:00:00</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -16749,12 +16749,12 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>-174.85</t>
+          <t>-169.71</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="BK31" t="inlineStr">
         <is>
-          <t>74266.29746835443</t>
+          <t>141867.7456140351</t>
         </is>
       </c>
       <c r="BL31" t="inlineStr">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>-4461.805521408209</t>
+          <t>-4461.805521410397</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>-9433.407593443422</t>
+          <t>-9433.40759344388</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
@@ -16854,17 +16854,17 @@
       </c>
       <c r="CC31" t="inlineStr">
         <is>
-          <t>8.92627718307661</t>
+          <t>-2.845366205615511</t>
         </is>
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>28.46535711116248</t>
+          <t>34.67288029195527</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>13.03574184015574</t>
+          <t>34.67288029195527</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>資訊服務業右上上櫃</t>
+          <t>資訊服務業平上櫃</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-02 00:00:00</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>1197977.30720339</t>
+          <t>1012585.318584071</t>
         </is>
       </c>
       <c r="BL32" t="inlineStr">
@@ -17328,12 +17328,12 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>-92209.1385105414</t>
+          <t>-92209.13851054321</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>-103422.9268219491</t>
+          <t>-103422.9268219495</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
@@ -17388,17 +17388,17 @@
       </c>
       <c r="CC32" t="inlineStr">
         <is>
-          <t>16.01701207901721</t>
+          <t>-8.707127354530044</t>
         </is>
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>262.8342491895248</t>
+          <t>309.3684733963202</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>127.8696834194544</t>
+          <t>309.3684733963202</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -17670,12 +17670,12 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-01-20 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -17817,12 +17817,12 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>-82.85</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>383683525.4113925</t>
+          <t>322337758.8450292</t>
         </is>
       </c>
       <c r="BL33" t="inlineStr">
@@ -17862,12 +17862,12 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>-13457182.38943072</t>
+          <t>-13457182.38944513</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
         <is>
-          <t>-20199013.65226176</t>
+          <t>-20199013.65226486</t>
         </is>
       </c>
       <c r="BS33" t="inlineStr">
@@ -17922,17 +17922,17 @@
       </c>
       <c r="CC33" t="inlineStr">
         <is>
-          <t>49.99614326485486</t>
+          <t>-21.90896156878878</t>
         </is>
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>-8.4883351568842</t>
+          <t>51.14983763338738</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>-26.81105813656552</t>
+          <t>51.14983763338738</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2025-10-29 00:00:00</t>
+          <t>2025-10-28 00:00:00</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>17455360.65822785</t>
+          <t>14257271.90058479</t>
         </is>
       </c>
       <c r="BL34" t="inlineStr">
@@ -18395,12 +18395,12 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>-476166.3491232005</t>
+          <t>-476166.349122265</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
         <is>
-          <t>-1050943.803362502</t>
+          <t>-1050943.803362302</t>
         </is>
       </c>
       <c r="BS34" t="inlineStr">
@@ -18455,17 +18455,17 @@
       </c>
       <c r="CC34" t="inlineStr">
         <is>
-          <t>-7.746406823998227</t>
+          <t>-17.07967221250178</t>
         </is>
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>9.676389054176088</t>
+          <t>2.351733911353025</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>17.84821486793678</t>
+          <t>2.351733911353025</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
@@ -18587,7 +18587,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>10454.50</t>
+          <t>10454.35</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
@@ -18883,12 +18883,12 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>-100.05</t>
+          <t>-100.03</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>599026183.8050847</t>
+          <t>685922189.8359375</t>
         </is>
       </c>
       <c r="BL35" t="inlineStr">
@@ -18928,12 +18928,12 @@
       </c>
       <c r="BQ35" t="inlineStr">
         <is>
-          <t>308332.2128152866</t>
+          <t>308332.2128302129</t>
         </is>
       </c>
       <c r="BR35" t="inlineStr">
         <is>
-          <t>-35169402.36628824</t>
+          <t>-35169402.36628497</t>
         </is>
       </c>
       <c r="BS35" t="inlineStr">
@@ -18988,17 +18988,17 @@
       </c>
       <c r="CC35" t="inlineStr">
         <is>
-          <t>-5.303234217820504</t>
+          <t>15.07289547155181</t>
         </is>
       </c>
       <c r="CD35" t="inlineStr">
         <is>
-          <t>3.537808082781394</t>
+          <t>11.76716445086586</t>
         </is>
       </c>
       <c r="CE35" t="inlineStr">
         <is>
-          <t>26.66286061008567</t>
+          <t>11.76716445086586</t>
         </is>
       </c>
       <c r="CF35" t="inlineStr">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-01-28 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>1541802024.607595</t>
+          <t>812372615.4853802</t>
         </is>
       </c>
       <c r="BL36" t="inlineStr">
@@ -19462,12 +19462,12 @@
       </c>
       <c r="BQ36" t="inlineStr">
         <is>
-          <t>-138086486.9732901</t>
+          <t>-138086486.9732932</t>
         </is>
       </c>
       <c r="BR36" t="inlineStr">
         <is>
-          <t>-217249562.9118422</t>
+          <t>-217249562.9118428</t>
         </is>
       </c>
       <c r="BS36" t="inlineStr">
@@ -19522,17 +19522,17 @@
       </c>
       <c r="CC36" t="inlineStr">
         <is>
-          <t>25.80258570598489</t>
+          <t>3.734583209771571</t>
         </is>
       </c>
       <c r="CD36" t="inlineStr">
         <is>
-          <t>48.37452349338245</t>
+          <t>45.38917530513036</t>
         </is>
       </c>
       <c r="CE36" t="inlineStr">
         <is>
-          <t>30.67354959640375</t>
+          <t>45.38917530513036</t>
         </is>
       </c>
       <c r="CF36" t="inlineStr">
@@ -19632,7 +19632,7 @@
       </c>
       <c r="CY36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CZ36" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-23 00:00:00</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="BK37" t="inlineStr">
         <is>
-          <t>3217243.125</t>
+          <t>1988100.512695312</t>
         </is>
       </c>
       <c r="BL37" t="inlineStr">
@@ -19998,12 +19998,12 @@
       </c>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>461743.0988745346</t>
+          <t>461743.0988745402</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
         <is>
-          <t>-23574.04191541672</t>
+          <t>-23574.04191541485</t>
         </is>
       </c>
       <c r="BS37" t="inlineStr">
@@ -20058,17 +20058,17 @@
       </c>
       <c r="CC37" t="inlineStr">
         <is>
-          <t>3.785697238541799</t>
+          <t>44.78107112219424</t>
         </is>
       </c>
       <c r="CD37" t="inlineStr">
         <is>
-          <t>101.2137592631138</t>
+          <t>198.9215913084794</t>
         </is>
       </c>
       <c r="CE37" t="inlineStr">
         <is>
-          <t>32.48414660649049</t>
+          <t>198.9215913084794</t>
         </is>
       </c>
       <c r="CF37" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -20245,7 +20245,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-30.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2025-09-08 00:00:00</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>98.47999999999999</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -20488,12 +20488,12 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>-122.58</t>
+          <t>-108.03</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="BK38" t="inlineStr">
         <is>
-          <t>279677.8797468354</t>
+          <t>208754.4064327485</t>
         </is>
       </c>
       <c r="BL38" t="inlineStr">
@@ -20533,12 +20533,12 @@
       </c>
       <c r="BQ38" t="inlineStr">
         <is>
-          <t>-465.6259227706917</t>
+          <t>-465.6259227003665</t>
         </is>
       </c>
       <c r="BR38" t="inlineStr">
         <is>
-          <t>-1933.572837676293</t>
+          <t>-1933.572837661217</t>
         </is>
       </c>
       <c r="BS38" t="inlineStr">
@@ -20593,17 +20593,17 @@
       </c>
       <c r="CC38" t="inlineStr">
         <is>
-          <t>1.133047388590597</t>
+          <t>32.41014582049702</t>
         </is>
       </c>
       <c r="CD38" t="inlineStr">
         <is>
-          <t>21.72195695107622</t>
+          <t>-29.21416474295455</t>
         </is>
       </c>
       <c r="CE38" t="inlineStr">
         <is>
-          <t>1.185291880885543</t>
+          <t>-29.21416474295455</t>
         </is>
       </c>
       <c r="CF38" t="inlineStr">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="CR38" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CS38" t="inlineStr">
@@ -20765,7 +20765,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -20790,7 +20790,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-02-15 00:00:00</t>
+          <t>2026-02-21 00:00:00</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -20875,12 +20875,12 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/28</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-02-11 00:00:00</t>
+          <t>2026-02-10 00:00:00</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
@@ -21020,12 +21020,12 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>-88.99</t>
+          <t>-89.23</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr">
@@ -21035,7 +21035,7 @@
       </c>
       <c r="BK39" t="inlineStr">
         <is>
-          <t>3080143145.329114</t>
+          <t>1794961506.621094</t>
         </is>
       </c>
       <c r="BL39" t="inlineStr">
@@ -21065,12 +21065,12 @@
       </c>
       <c r="BQ39" t="inlineStr">
         <is>
-          <t>21056306.24023474</t>
+          <t>21056306.24021269</t>
         </is>
       </c>
       <c r="BR39" t="inlineStr">
         <is>
-          <t>413114914.5748577</t>
+          <t>413114914.5748525</t>
         </is>
       </c>
       <c r="BS39" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="BT39" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="BU39" t="inlineStr">
@@ -21125,17 +21125,17 @@
       </c>
       <c r="CC39" t="inlineStr">
         <is>
-          <t>13.97932716503426</t>
+          <t>7.534349425632555</t>
         </is>
       </c>
       <c r="CD39" t="inlineStr">
         <is>
-          <t>61.01861766432938</t>
+          <t>119.5660108771033</t>
         </is>
       </c>
       <c r="CE39" t="inlineStr">
         <is>
-          <t>95.35147736868528</t>
+          <t>119.5660108771033</t>
         </is>
       </c>
       <c r="CF39" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-02-15 00:00:00</t>
+          <t>2026-02-21 00:00:00</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -21407,12 +21407,12 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/01/02</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="BK40" t="inlineStr">
         <is>
-          <t>10696601959.93038</t>
+          <t>10674577358.4883</t>
         </is>
       </c>
       <c r="BL40" t="inlineStr">
@@ -21597,12 +21597,12 @@
       </c>
       <c r="BQ40" t="inlineStr">
         <is>
-          <t>492451658.5157425</t>
+          <t>492451658.5156305</t>
         </is>
       </c>
       <c r="BR40" t="inlineStr">
         <is>
-          <t>-305598602.703743</t>
+          <t>-305598602.7037659</t>
         </is>
       </c>
       <c r="BS40" t="inlineStr">
@@ -21612,7 +21612,7 @@
       </c>
       <c r="BT40" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="BU40" t="inlineStr">
@@ -21652,22 +21652,22 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CC40" t="inlineStr">
         <is>
-          <t>-19.79587786154143</t>
+          <t>21.96488082544542</t>
         </is>
       </c>
       <c r="CD40" t="inlineStr">
         <is>
-          <t>110.2422828598362</t>
+          <t>150.011681993923</t>
         </is>
       </c>
       <c r="CE40" t="inlineStr">
         <is>
-          <t>94.5886846859622</t>
+          <t>150.011681993923</t>
         </is>
       </c>
       <c r="CF40" t="inlineStr">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>2025-06-25 00:00:00</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -21859,17 +21859,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-16 00:00:00</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -21884,12 +21884,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>80.14000000000001</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
@@ -22084,12 +22084,12 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>-122.96</t>
+          <t>-122.74</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="BK41" t="inlineStr">
         <is>
-          <t>1356.935897435897</t>
+          <t>1464.333661417323</t>
         </is>
       </c>
       <c r="BL41" t="inlineStr">
@@ -22129,12 +22129,12 @@
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>-111.6708036097623</t>
+          <t>-111.6708036097706</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
         <is>
-          <t>-105.050861120568</t>
+          <t>-105.0508611205698</t>
         </is>
       </c>
       <c r="BS41" t="inlineStr">
@@ -22189,17 +22189,17 @@
       </c>
       <c r="CC41" t="inlineStr">
         <is>
-          <t>2.587435531995612</t>
+          <t>5.97786162264811</t>
         </is>
       </c>
       <c r="CD41" t="inlineStr">
         <is>
-          <t>0.9183796978071856</t>
+          <t>3.480632789093074</t>
         </is>
       </c>
       <c r="CE41" t="inlineStr">
         <is>
-          <t>5.728156723751122</t>
+          <t>3.480632789093074</t>
         </is>
       </c>
       <c r="CF41" t="inlineStr">
@@ -22391,12 +22391,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-01-08 00:00:00</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-01-13 00:00:00</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -22416,12 +22416,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -22576,12 +22576,12 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>73.07000000000001</t>
+          <t>73.07</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>73.93</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>77.434</t>
+          <t>77.43400000000001</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
@@ -22616,12 +22616,12 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>-161.79</t>
+          <t>-136.10</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="BK42" t="inlineStr">
         <is>
-          <t>9192955.0</t>
+          <t>26870650.81690141</t>
         </is>
       </c>
       <c r="BL42" t="inlineStr">
@@ -22661,12 +22661,12 @@
       </c>
       <c r="BQ42" t="inlineStr">
         <is>
-          <t>-1307320.758142424</t>
+          <t>-1307320.758141014</t>
         </is>
       </c>
       <c r="BR42" t="inlineStr">
         <is>
-          <t>-613361.3855471592</t>
+          <t>-613361.3855468575</t>
         </is>
       </c>
       <c r="BS42" t="inlineStr">
@@ -22721,17 +22721,17 @@
       </c>
       <c r="CC42" t="inlineStr">
         <is>
-          <t>0.9041404778179756</t>
+          <t>0.5309937389828093</t>
         </is>
       </c>
       <c r="CD42" t="inlineStr">
         <is>
-          <t>11.41353245049875</t>
+          <t>14.86441841861211</t>
         </is>
       </c>
       <c r="CE42" t="inlineStr">
         <is>
-          <t>11.89857857932097</t>
+          <t>14.86441841861211</t>
         </is>
       </c>
       <c r="CF42" t="inlineStr">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2025-08-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
@@ -23148,12 +23148,12 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>-120.54</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="BK43" t="inlineStr">
         <is>
-          <t>15194.76582278481</t>
+          <t>9757.982456140351</t>
         </is>
       </c>
       <c r="BL43" t="inlineStr">
@@ -23193,12 +23193,12 @@
       </c>
       <c r="BQ43" t="inlineStr">
         <is>
-          <t>38.77330843603244</t>
+          <t>38.77330843750699</t>
         </is>
       </c>
       <c r="BR43" t="inlineStr">
         <is>
-          <t>-123.5451157126054</t>
+          <t>-123.5451157122889</t>
         </is>
       </c>
       <c r="BS43" t="inlineStr">
@@ -23253,17 +23253,17 @@
       </c>
       <c r="CC43" t="inlineStr">
         <is>
-          <t>7.201621378171446</t>
+          <t>3.542369795678295</t>
         </is>
       </c>
       <c r="CD43" t="inlineStr">
         <is>
-          <t>23.17976185855554</t>
+          <t>22.99074282007136</t>
         </is>
       </c>
       <c r="CE43" t="inlineStr">
         <is>
-          <t>20.09503681720145</t>
+          <t>22.99074282007136</t>
         </is>
       </c>
       <c r="CF43" t="inlineStr">
@@ -23328,7 +23328,7 @@
       </c>
       <c r="CR43" t="inlineStr">
         <is>
-          <t>觀光事業右下上櫃</t>
+          <t>觀光事業平上櫃</t>
         </is>
       </c>
       <c r="CS43" t="inlineStr">
@@ -23565,7 +23565,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2025-10-09 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -23695,7 +23695,7 @@
       </c>
       <c r="BK44" t="inlineStr">
         <is>
-          <t>2284.965957446809</t>
+          <t>2720.847826086957</t>
         </is>
       </c>
       <c r="BL44" t="inlineStr">
@@ -23725,12 +23725,12 @@
       </c>
       <c r="BQ44" t="inlineStr">
         <is>
-          <t>73.28617007438189</t>
+          <t>73.28617007437046</t>
         </is>
       </c>
       <c r="BR44" t="inlineStr">
         <is>
-          <t>339.9421670555116</t>
+          <t>339.9421670555093</t>
         </is>
       </c>
       <c r="BS44" t="inlineStr">
@@ -23785,17 +23785,17 @@
       </c>
       <c r="CC44" t="inlineStr">
         <is>
-          <t>5.737494922985597</t>
+          <t>-3.243763924428397</t>
         </is>
       </c>
       <c r="CD44" t="inlineStr">
         <is>
-          <t>28.63713073753668</t>
+          <t>22.24893601134921</t>
         </is>
       </c>
       <c r="CE44" t="inlineStr">
         <is>
-          <t>27.45289209577288</t>
+          <t>22.24893601134921</t>
         </is>
       </c>
       <c r="CF44" t="inlineStr">
@@ -23972,37 +23972,37 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-05-23 00:00:00</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-09 00:00:00</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-12-27 00:00:00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-12-30 00:00:00</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>237.5</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -24027,12 +24027,12 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2025-09-15 00:00:00</t>
+          <t>2025-08-13 00:00:00</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
@@ -24212,12 +24212,12 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>-105.72</t>
+          <t>-105.67</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr">
@@ -24227,7 +24227,7 @@
       </c>
       <c r="BK45" t="inlineStr">
         <is>
-          <t>152385212.5759494</t>
+          <t>197749574.8304093</t>
         </is>
       </c>
       <c r="BL45" t="inlineStr">
@@ -24257,12 +24257,12 @@
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>-1205403.064541849</t>
+          <t>-1205403.064542181</t>
         </is>
       </c>
       <c r="BR45" t="inlineStr">
         <is>
-          <t>-3225626.184763059</t>
+          <t>-3225626.184763141</t>
         </is>
       </c>
       <c r="BS45" t="inlineStr">
@@ -24317,17 +24317,17 @@
       </c>
       <c r="CC45" t="inlineStr">
         <is>
-          <t>5.340846863039838</t>
+          <t>2.994484852874964</t>
         </is>
       </c>
       <c r="CD45" t="inlineStr">
         <is>
-          <t>7.396496187805554</t>
+          <t>-1.715991676206982</t>
         </is>
       </c>
       <c r="CE45" t="inlineStr">
         <is>
-          <t>5.41021697141371</t>
+          <t>-1.715991676206982</t>
         </is>
       </c>
       <c r="CF45" t="inlineStr">
@@ -24449,7 +24449,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -24509,32 +24509,32 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-21 00:00:00</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-23 00:00:00</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-03 00:00:00</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -24544,12 +24544,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -24559,12 +24559,12 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.54</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -24629,7 +24629,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-09-11 00:00:00</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
@@ -24744,12 +24744,12 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>-125.63</t>
+          <t>-108.96</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr">
@@ -24759,7 +24759,7 @@
       </c>
       <c r="BK46" t="inlineStr">
         <is>
-          <t>2319966.550632911</t>
+          <t>4111622.409356725</t>
         </is>
       </c>
       <c r="BL46" t="inlineStr">
@@ -24789,12 +24789,12 @@
       </c>
       <c r="BQ46" t="inlineStr">
         <is>
-          <t>65949.75037579043</t>
+          <t>65949.7503757228</t>
         </is>
       </c>
       <c r="BR46" t="inlineStr">
         <is>
-          <t>62563.41294333618</t>
+          <t>62563.41294332175</t>
         </is>
       </c>
       <c r="BS46" t="inlineStr">
@@ -24849,17 +24849,17 @@
       </c>
       <c r="CC46" t="inlineStr">
         <is>
-          <t>2.333575100122986</t>
+          <t>-8.797879880435117</t>
         </is>
       </c>
       <c r="CD46" t="inlineStr">
         <is>
-          <t>1.983029541169076</t>
+          <t>5.207777896271018</t>
         </is>
       </c>
       <c r="CE46" t="inlineStr">
         <is>
-          <t>5.910997839153195</t>
+          <t>5.207777896271018</t>
         </is>
       </c>
       <c r="CF46" t="inlineStr">
@@ -25021,7 +25021,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -25051,12 +25051,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-06 00:00:00</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -25076,12 +25076,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.09</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2025-08-07 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -25297,7 +25297,7 @@
       </c>
       <c r="BK47" t="inlineStr">
         <is>
-          <t>377964916.113924</t>
+          <t>427323282.6900585</t>
         </is>
       </c>
       <c r="BL47" t="inlineStr">
@@ -25327,12 +25327,12 @@
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>-10694958.1154364</t>
+          <t>-10694958.11543477</t>
         </is>
       </c>
       <c r="BR47" t="inlineStr">
         <is>
-          <t>-19408141.312508</t>
+          <t>-19408141.31250763</t>
         </is>
       </c>
       <c r="BS47" t="inlineStr">
@@ -25387,17 +25387,17 @@
       </c>
       <c r="CC47" t="inlineStr">
         <is>
-          <t>9.863952768508312</t>
+          <t>1.353498369974546</t>
         </is>
       </c>
       <c r="CD47" t="inlineStr">
         <is>
-          <t>25.97581583467228</t>
+          <t>37.80187910634068</t>
         </is>
       </c>
       <c r="CE47" t="inlineStr">
         <is>
-          <t>12.65673535952737</t>
+          <t>37.80187910634068</t>
         </is>
       </c>
       <c r="CF47" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-02-15 00:00:00</t>
+          <t>2026-02-21 00:00:00</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -25639,12 +25639,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/05/13</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>674.0</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>595.0</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-01-23 00:00:00</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -25829,7 +25829,7 @@
       </c>
       <c r="BK48" t="inlineStr">
         <is>
-          <t>7583305750.601266</t>
+          <t>5999489251.777778</t>
         </is>
       </c>
       <c r="BL48" t="inlineStr">
@@ -25859,12 +25859,12 @@
       </c>
       <c r="BQ48" t="inlineStr">
         <is>
-          <t>546085505.8939428</t>
+          <t>546085505.8938491</t>
         </is>
       </c>
       <c r="BR48" t="inlineStr">
         <is>
-          <t>687894794.9043655</t>
+          <t>687894794.9043465</t>
         </is>
       </c>
       <c r="BS48" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="BT48" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="BU48" t="inlineStr">
@@ -25919,17 +25919,17 @@
       </c>
       <c r="CC48" t="inlineStr">
         <is>
-          <t>7.079898360562166</t>
+          <t>24.79062369107497</t>
         </is>
       </c>
       <c r="CD48" t="inlineStr">
         <is>
-          <t>35.79294772774711</t>
+          <t>55.48609183706041</t>
         </is>
       </c>
       <c r="CE48" t="inlineStr">
         <is>
-          <t>46.38645342474714</t>
+          <t>55.48609183706041</t>
         </is>
       </c>
       <c r="CF48" t="inlineStr">
@@ -26051,7 +26051,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -26091,7 +26091,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -26106,7 +26106,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-02-15 00:00:00</t>
+          <t>2026-02-21 00:00:00</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -26171,12 +26171,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/05/15</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -26201,12 +26201,12 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/13</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226.5</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
@@ -26361,7 +26361,7 @@
       </c>
       <c r="BK49" t="inlineStr">
         <is>
-          <t>6646496292.120253</t>
+          <t>4502374214.467836</t>
         </is>
       </c>
       <c r="BL49" t="inlineStr">
@@ -26391,12 +26391,12 @@
       </c>
       <c r="BQ49" t="inlineStr">
         <is>
-          <t>243739929.6897638</t>
+          <t>243739929.6897047</t>
         </is>
       </c>
       <c r="BR49" t="inlineStr">
         <is>
-          <t>355155423.5897894</t>
+          <t>355155423.589777</t>
         </is>
       </c>
       <c r="BS49" t="inlineStr">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="BT49" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="BU49" t="inlineStr">
@@ -26451,17 +26451,17 @@
       </c>
       <c r="CC49" t="inlineStr">
         <is>
-          <t>-3.7966775266639</t>
+          <t>14.6647704735203</t>
         </is>
       </c>
       <c r="CD49" t="inlineStr">
         <is>
-          <t>46.34323301800399</t>
+          <t>68.54400099518323</t>
         </is>
       </c>
       <c r="CE49" t="inlineStr">
         <is>
-          <t>54.01889447891342</t>
+          <t>68.54400099518323</t>
         </is>
       </c>
       <c r="CF49" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-30.0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
@@ -26878,139 +26878,139 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
+          <t>6.33</t>
+        </is>
+      </c>
+      <c r="BI50" t="inlineStr">
+        <is>
+          <t>-88.04</t>
+        </is>
+      </c>
+      <c r="BJ50" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="BK50" t="inlineStr">
+        <is>
+          <t>1495735283.18504</t>
+        </is>
+      </c>
+      <c r="BL50" t="inlineStr">
+        <is>
+          <t>1123605557.0</t>
+        </is>
+      </c>
+      <c r="BM50" t="inlineStr">
+        <is>
+          <t>523640982.2</t>
+        </is>
+      </c>
+      <c r="BN50" t="inlineStr">
+        <is>
+          <t>497418736.4</t>
+        </is>
+      </c>
+      <c r="BO50" t="inlineStr">
+        <is>
+          <t>485150717.8</t>
+        </is>
+      </c>
+      <c r="BP50" t="inlineStr">
+        <is>
+          <t>26222245</t>
+        </is>
+      </c>
+      <c r="BQ50" t="inlineStr">
+        <is>
+          <t>7702484.281969444</t>
+        </is>
+      </c>
+      <c r="BR50" t="inlineStr">
+        <is>
+          <t>-41688492.54222143</t>
+        </is>
+      </c>
+      <c r="BS50" t="inlineStr">
+        <is>
+          <t>1123605557.0</t>
+        </is>
+      </c>
+      <c r="BT50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU50" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="BV50" t="inlineStr">
+        <is>
+          <t>2026/01/22</t>
+        </is>
+      </c>
+      <c r="BW50" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="BX50" t="inlineStr">
+        <is>
+          <t>矽統</t>
+        </is>
+      </c>
+      <c r="BY50" t="inlineStr">
+        <is>
+          <t>矽統</t>
+        </is>
+      </c>
+      <c r="BZ50" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="CA50" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="CB50" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="CC50" t="inlineStr">
+        <is>
+          <t>66.23063912423848</t>
+        </is>
+      </c>
+      <c r="CD50" t="inlineStr">
+        <is>
+          <t>171.5841926157153</t>
+        </is>
+      </c>
+      <c r="CE50" t="inlineStr">
+        <is>
+          <t>171.5841926157153</t>
+        </is>
+      </c>
+      <c r="CF50" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CG50" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="CH50" t="inlineStr">
+        <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="BI50" t="inlineStr">
-        <is>
-          <t>-53.94</t>
-        </is>
-      </c>
-      <c r="BJ50" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="BK50" t="inlineStr">
-        <is>
-          <t>609604770.7341772</t>
-        </is>
-      </c>
-      <c r="BL50" t="inlineStr">
-        <is>
-          <t>1123605557.0</t>
-        </is>
-      </c>
-      <c r="BM50" t="inlineStr">
-        <is>
-          <t>523640982.2</t>
-        </is>
-      </c>
-      <c r="BN50" t="inlineStr">
-        <is>
-          <t>497418736.4</t>
-        </is>
-      </c>
-      <c r="BO50" t="inlineStr">
-        <is>
-          <t>485150717.8</t>
-        </is>
-      </c>
-      <c r="BP50" t="inlineStr">
-        <is>
-          <t>26222245</t>
-        </is>
-      </c>
-      <c r="BQ50" t="inlineStr">
-        <is>
-          <t>7702484.281963001</t>
-        </is>
-      </c>
-      <c r="BR50" t="inlineStr">
-        <is>
-          <t>-41688492.54222286</t>
-        </is>
-      </c>
-      <c r="BS50" t="inlineStr">
-        <is>
-          <t>1123605557.0</t>
-        </is>
-      </c>
-      <c r="BT50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU50" t="inlineStr">
-        <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="BV50" t="inlineStr">
-        <is>
-          <t>2026/01/22</t>
-        </is>
-      </c>
-      <c r="BW50" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="BX50" t="inlineStr">
-        <is>
-          <t>矽統</t>
-        </is>
-      </c>
-      <c r="BY50" t="inlineStr">
-        <is>
-          <t>矽統</t>
-        </is>
-      </c>
-      <c r="BZ50" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="CA50" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="CB50" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="CC50" t="inlineStr">
-        <is>
-          <t>5.548691034568258</t>
-        </is>
-      </c>
-      <c r="CD50" t="inlineStr">
-        <is>
-          <t>159.5149310600596</t>
-        </is>
-      </c>
-      <c r="CE50" t="inlineStr">
-        <is>
-          <t>281.9780383448873</t>
-        </is>
-      </c>
-      <c r="CF50" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CG50" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="CH50" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
       <c r="CI50" t="inlineStr">
         <is>
           <t>0.91</t>
@@ -27058,7 +27058,7 @@
       </c>
       <c r="CR50" t="inlineStr">
         <is>
-          <t>半導體業右上上市</t>
+          <t>半導體業平上市</t>
         </is>
       </c>
       <c r="CS50" t="inlineStr">
@@ -27155,7 +27155,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-02-15 00:00:00</t>
+          <t>2026-02-21 00:00:00</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -27265,12 +27265,12 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/20</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
@@ -27295,7 +27295,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>2026-02-10 00:00:00</t>
+          <t>2026-02-09 00:00:00</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
@@ -27410,7 +27410,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>60.81</t>
+          <t>60.79</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
@@ -27425,7 +27425,7 @@
       </c>
       <c r="BK51" t="inlineStr">
         <is>
-          <t>7276135341.322784</t>
+          <t>5335415354.391813</t>
         </is>
       </c>
       <c r="BL51" t="inlineStr">
@@ -27455,12 +27455,12 @@
       </c>
       <c r="BQ51" t="inlineStr">
         <is>
-          <t>186186662.2342376</t>
+          <t>186186662.2342147</t>
         </is>
       </c>
       <c r="BR51" t="inlineStr">
         <is>
-          <t>933243518.2280769</t>
+          <t>933243518.2280722</t>
         </is>
       </c>
       <c r="BS51" t="inlineStr">
@@ -27470,7 +27470,7 @@
       </c>
       <c r="BT51" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="BU51" t="inlineStr">
@@ -27515,17 +27515,17 @@
       </c>
       <c r="CC51" t="inlineStr">
         <is>
-          <t>15.51032482408811</t>
+          <t>-17.36962644891114</t>
         </is>
       </c>
       <c r="CD51" t="inlineStr">
         <is>
-          <t>67.64586174209458</t>
+          <t>71.87173035181205</t>
         </is>
       </c>
       <c r="CE51" t="inlineStr">
         <is>
-          <t>124.8349898823401</t>
+          <t>71.87173035181205</t>
         </is>
       </c>
       <c r="CF51" t="inlineStr">
@@ -27687,7 +27687,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -27702,7 +27702,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -27797,12 +27797,12 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/14</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>401.0</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>2026-02-11 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
@@ -28015,7 +28015,7 @@
       </c>
       <c r="BK52" t="inlineStr">
         <is>
-          <t>13161779506.31013</t>
+          <t>9050099407.760235</t>
         </is>
       </c>
       <c r="BL52" t="inlineStr">
@@ -28045,12 +28045,12 @@
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
-          <t>54374674.64585207</t>
+          <t>54374674.64593329</t>
         </is>
       </c>
       <c r="BR52" t="inlineStr">
         <is>
-          <t>-114301148.5346069</t>
+          <t>-114301148.5345879</t>
         </is>
       </c>
       <c r="BS52" t="inlineStr">
@@ -28105,17 +28105,17 @@
       </c>
       <c r="CC52" t="inlineStr">
         <is>
-          <t>6.21790530768367</t>
+          <t>-7.471056079739009</t>
         </is>
       </c>
       <c r="CD52" t="inlineStr">
         <is>
-          <t>38.58583304817382</t>
+          <t>32.87285305984144</t>
         </is>
       </c>
       <c r="CE52" t="inlineStr">
         <is>
-          <t>31.75552339723058</t>
+          <t>32.87285305984144</t>
         </is>
       </c>
       <c r="CF52" t="inlineStr">
@@ -28215,7 +28215,7 @@
       </c>
       <c r="CY52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CZ52" t="inlineStr">
@@ -28277,7 +28277,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -28357,12 +28357,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/02/18</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1855.0</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -28387,12 +28387,12 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/11</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1455.0</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
@@ -28417,7 +28417,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>2026-01-20 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
@@ -28533,12 +28533,12 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>200.76</t>
+          <t>200.81</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>-155.89</t>
+          <t>-155.88</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="BK53" t="inlineStr">
         <is>
-          <t>3782220887.240506</t>
+          <t>3090113405.426901</t>
         </is>
       </c>
       <c r="BL53" t="inlineStr">
@@ -28578,12 +28578,12 @@
       </c>
       <c r="BQ53" t="inlineStr">
         <is>
-          <t>-90285100.01350772</t>
+          <t>-90285100.01353636</t>
         </is>
       </c>
       <c r="BR53" t="inlineStr">
         <is>
-          <t>-233676392.1679072</t>
+          <t>-233676392.1679134</t>
         </is>
       </c>
       <c r="BS53" t="inlineStr">
@@ -28598,17 +28598,17 @@
       </c>
       <c r="BU53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="BV53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/05/15</t>
         </is>
       </c>
       <c r="BW53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.50</t>
         </is>
       </c>
       <c r="BX53" t="inlineStr">
@@ -28638,17 +28638,17 @@
       </c>
       <c r="CC53" t="inlineStr">
         <is>
-          <t>3.803120261693147</t>
+          <t>3.048033185192066</t>
         </is>
       </c>
       <c r="CD53" t="inlineStr">
         <is>
-          <t>53.46382925644944</t>
+          <t>43.90302236267866</t>
         </is>
       </c>
       <c r="CE53" t="inlineStr">
         <is>
-          <t>72.77257334933576</t>
+          <t>43.90302236267866</t>
         </is>
       </c>
       <c r="CF53" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="CR53" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CS53" t="inlineStr">

--- a/Result/checkGreat.xlsx
+++ b/Result/checkGreat.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>70324.97076023392</t>
+          <t>118287.1835443038</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>-30626.34535433455</t>
+          <t>-30626.34535433344</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-28853.4834537281</t>
+          <t>-28853.48345372784</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2024-12-05 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2024-12-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-09-11 00:00:00</t>
+          <t>2026-01-30 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-109.65</t>
+          <t>-132.07</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>50150.29824561403</t>
+          <t>20568.78481012658</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2564.558961187478</t>
+          <t>2564.558961188781</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>7289.045912995825</t>
+          <t>7289.045912996105</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-06-09 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-06-12 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-09-15 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-107.28</t>
+          <t>-109.13</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>60151.52357563851</t>
+          <t>34623.79113924051</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-1887.668728227026</t>
+          <t>-1887.668728227526</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-1630.541628296995</t>
+          <t>-1630.541628297102</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-120.77</t>
+          <t>-130.53</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>2376346251.406433</t>
+          <t>2345603540.234177</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
@@ -2928,12 +2928,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-217253314.961409</t>
+          <t>-217253314.9614288</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-213128712.1573748</t>
+          <t>-213128712.1573791</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025/02/20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3260,22 +3260,22 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2025/03/17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2024/11/27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-02-11 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>1740067689.80117</t>
+          <t>3653881091.550632</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-535341824.513673</t>
+          <t>-535341824.5136742</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-02-21 00:00:00</t>
+          <t>2026-02-22 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-02-21 00:00:00</t>
+          <t>2026-02-22 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>263803.550209205</t>
+          <t>258125.1772151898</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>125425.3425555268</t>
+          <t>125425.342555576</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>151915.6932864046</t>
+          <t>151915.6932864152</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-08-06 00:00:00</t>
+          <t>2025-08-05 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>82.12</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-130.20</t>
+          <t>-200.31</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>278291836.7275862</t>
+          <t>248664913.4050633</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>5856764.418786909</t>
+          <t>5856764.418776231</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-2610085.531445786</t>
+          <t>-2610085.531448081</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-09-12 00:00:00</t>
+          <t>2026-01-19 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-147.09</t>
+          <t>-147.14</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>3775.065789473684</t>
+          <t>2376.164556962025</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>24.16218418197378</t>
+          <t>24.16218418196721</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>286.6945559064161</t>
+          <t>286.6945559064143</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5844,32 +5844,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-06-11 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-06-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-04-01 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-10-23 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-79.48</t>
+          <t>-60.01</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>4231912.334558824</t>
+          <t>2584123.563291139</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>40411.60306678298</t>
+          <t>40411.60306664033</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-58852.390435518</t>
+          <t>-58852.3904355485</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-01-26 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>77.63000000000001</t>
+          <t>77.63</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-67.17</t>
+          <t>-42.27</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>6176719.877777778</t>
+          <t>5500160.20886076</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>-61536.44969778304</t>
+          <t>-61536.44969822086</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>-800957.0055001881</t>
+          <t>-800957.0055002831</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>-122.02</t>
+          <t>-146.27</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="BK13" t="inlineStr">
         <is>
-          <t>58264.59064327485</t>
+          <t>59698.74050632911</t>
         </is>
       </c>
       <c r="BL13" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>42.05045897559836</t>
+          <t>42.05045897682515</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2121.524995664175</t>
+          <t>2121.524995664437</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-103.44</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="BK14" t="inlineStr">
         <is>
-          <t>112238.0945945946</t>
+          <t>115739.0696202532</t>
         </is>
       </c>
       <c r="BL14" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>-1.137025915126273</t>
+          <t>-1.137025918107852</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>530.2182921629101</t>
+          <t>530.2182921622734</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-30.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024/12/30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025/02/11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>27.06</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>-113.52</t>
+          <t>-116.91</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>112382.418128655</t>
+          <t>115913.7278481013</t>
         </is>
       </c>
       <c r="BL15" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>-2057.640235590873</t>
+          <t>-2057.64023559072</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>-4244.023537209599</t>
+          <t>-4244.02353720957</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>半導體業平上櫃</t>
+          <t>半導體業右下上櫃</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-05-14 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2025-05-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>245.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>-118.97</t>
+          <t>-123.37</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="BK16" t="inlineStr">
         <is>
-          <t>2937.865795724466</t>
+          <t>2055.197872340425</t>
         </is>
       </c>
       <c r="BL16" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>-71.72467694705652</t>
+          <t>-71.72467694707807</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>-78.32072664336022</t>
+          <t>-78.32072664336488</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-02-21 00:00:00</t>
+          <t>2026-02-22 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>-49.25</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>256801117.9035088</t>
+          <t>184363370.5696203</t>
         </is>
       </c>
       <c r="BL17" t="inlineStr">
@@ -9319,12 +9319,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>114275159.6406179</t>
+          <t>114275159.6406137</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>176279027.5003502</t>
+          <t>176279027.5003492</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025/03/12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>786.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025/04/07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>526.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-01-22 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>2975771934.030488</t>
+          <t>4025566519.138889</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>10187989.86008374</t>
+          <t>10187989.86018615</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>-167757068.1046653</t>
+          <t>-167757068.1046429</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-02-21 00:00:00</t>
+          <t>2026-02-22 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025/05/15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>261.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-01-28 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="BK19" t="inlineStr">
         <is>
-          <t>441302.4433427762</t>
+          <t>587340.753164557</t>
         </is>
       </c>
       <c r="BL19" t="inlineStr">
@@ -10400,12 +10400,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>4624.325919375975</t>
+          <t>4624.325919379853</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>-72228.96030906658</t>
+          <t>-72228.96030906565</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024/10/23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2045.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025/02/11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2225.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-01-22 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="BK20" t="inlineStr">
         <is>
-          <t>8065945061.009146</t>
+          <t>8889587854.652777</t>
         </is>
       </c>
       <c r="BL20" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>-372941384.4185039</t>
+          <t>-372941384.418655</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>-443045469.888135</t>
+          <t>-443045469.8881664</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10954,17 +10954,17 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>2150.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>2025/05/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -11421,12 +11421,12 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>59.07</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>-55.72</t>
+          <t>-51.41</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>586702.418128655</t>
+          <t>484273.2784810127</t>
         </is>
       </c>
       <c r="BL21" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>-28028.56525624707</t>
+          <t>-28028.56525623871</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>-59464.02065674408</t>
+          <t>-59464.02065674221</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>-140.52</t>
+          <t>-139.78</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>37468.06666666667</t>
+          <t>22988.17088607595</t>
         </is>
       </c>
       <c r="BL22" t="inlineStr">
@@ -11999,12 +11999,12 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>-56.69943366189632</t>
+          <t>-56.69943366206223</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>587.177710001848</t>
+          <t>587.1777100018116</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-11-04 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="BK23" t="inlineStr">
         <is>
-          <t>106319.201754386</t>
+          <t>166681.3481012658</t>
         </is>
       </c>
       <c r="BL23" t="inlineStr">
@@ -12531,12 +12531,12 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>3373.104127408323</t>
+          <t>3373.104127409665</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2402.095965494831</t>
+          <t>2402.095965495122</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -12783,32 +12783,32 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2024-11-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2024-11-28 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2024-05-31 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2024-06-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -12818,12 +12818,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>190.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>177.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -12833,12 +12833,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-21.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>-10.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-08-15 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>-108.91</t>
+          <t>-151.55</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>18997.70175438597</t>
+          <t>11195.90506329114</t>
         </is>
       </c>
       <c r="BL24" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>10.51296958540646</t>
+          <t>10.51296958536456</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>-104.4730236547716</t>
+          <t>-104.4730236547798</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>99.126</t>
+          <t>99.12599999999999</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>-113.62</t>
+          <t>-134.46</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="BK25" t="inlineStr">
         <is>
-          <t>39435.78235294118</t>
+          <t>63155.68987341772</t>
         </is>
       </c>
       <c r="BL25" t="inlineStr">
@@ -13595,12 +13595,12 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>-5265.120946099207</t>
+          <t>-5265.120946098223</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>-7377.549500694691</t>
+          <t>-7377.549500694495</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>其他右上上櫃</t>
+          <t>其他右下上櫃</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="BK26" t="inlineStr">
         <is>
-          <t>56057.45321637427</t>
+          <t>50138.10759493671</t>
         </is>
       </c>
       <c r="BL26" t="inlineStr">
@@ -14127,12 +14127,12 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>4393.64736242373</t>
+          <t>4393.647362424173</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>-7892.046400155697</t>
+          <t>-7892.046400155552</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CZ26" t="inlineStr">
@@ -14374,37 +14374,37 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2025-05-15 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2025-06-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-01-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2025-02-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -14414,114 +14414,114 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025/05/16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026/02/03</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>98.2</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
           <t>138.5</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>-37.60</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025/05/16</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>97.4</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2025-09-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2026/02/03</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>98.2</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>138.5</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>97.4</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AP27" t="inlineStr">
         <is>
           <t>生技醫療｜下游｜醫療器材代理銷售及通路</t>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>98.46000000000001</t>
+          <t>98.46</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>99.22200000000001</t>
+          <t>99.222</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -14614,12 +14614,12 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>-105.45</t>
+          <t>-105.86</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="BK27" t="inlineStr">
         <is>
-          <t>20139.99707602339</t>
+          <t>20818.53164556962</t>
         </is>
       </c>
       <c r="BL27" t="inlineStr">
@@ -14659,12 +14659,12 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>-280.4544118228381</t>
+          <t>-280.4544118250262</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>-508.8858880139987</t>
+          <t>-508.885888014468</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-10-08 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="BK28" t="inlineStr">
         <is>
-          <t>965054.7953216375</t>
+          <t>1785888.816455696</t>
         </is>
       </c>
       <c r="BL28" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>90039.4654463361</t>
+          <t>90039.4654463207</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>30279.62277978659</t>
+          <t>30279.62277978286</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
@@ -15682,12 +15682,12 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>-124.21</t>
+          <t>-124.30</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="BK29" t="inlineStr">
         <is>
-          <t>549737132.745614</t>
+          <t>811443049.0189873</t>
         </is>
       </c>
       <c r="BL29" t="inlineStr">
@@ -15727,12 +15727,12 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>-19367339.49049809</t>
+          <t>-19367339.49049051</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>-24408827.57121426</t>
+          <t>-24408827.57121262</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -16214,12 +16214,12 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>118.41</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-84.21</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="BK30" t="inlineStr">
         <is>
-          <t>2619934302.98538</t>
+          <t>2010746562.879747</t>
         </is>
       </c>
       <c r="BL30" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>-101770307.9914492</t>
+          <t>-101770307.9914007</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>-200753984.7942836</t>
+          <t>-200753984.7942731</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -16749,12 +16749,12 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>-169.71</t>
+          <t>-174.85</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="BK31" t="inlineStr">
         <is>
-          <t>141867.7456140351</t>
+          <t>74266.29746835443</t>
         </is>
       </c>
       <c r="BL31" t="inlineStr">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>-4461.805521410397</t>
+          <t>-4461.805521408209</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>-9433.40759344388</t>
+          <t>-9433.407593443422</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-01-02 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>1012585.318584071</t>
+          <t>1197977.30720339</t>
         </is>
       </c>
       <c r="BL32" t="inlineStr">
@@ -17328,12 +17328,12 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>-92209.13851054321</t>
+          <t>-92209.1385105414</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>-103422.9268219495</t>
+          <t>-103422.9268219491</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -17670,12 +17670,12 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025/04/09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-20 00:00:00</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -17817,12 +17817,12 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>-91.79</t>
+          <t>-82.85</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>322337758.8450292</t>
+          <t>383683525.4113925</t>
         </is>
       </c>
       <c r="BL33" t="inlineStr">
@@ -17862,12 +17862,12 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>-13457182.38944513</t>
+          <t>-13457182.38943072</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
         <is>
-          <t>-20199013.65226486</t>
+          <t>-20199013.65226176</t>
         </is>
       </c>
       <c r="BS33" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2025-10-28 00:00:00</t>
+          <t>2025-10-29 00:00:00</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>14257271.90058479</t>
+          <t>17455360.65822785</t>
         </is>
       </c>
       <c r="BL34" t="inlineStr">
@@ -18395,12 +18395,12 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>-476166.349122265</t>
+          <t>-476166.3491232005</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
         <is>
-          <t>-1050943.803362302</t>
+          <t>-1050943.803362502</t>
         </is>
       </c>
       <c r="BS34" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>10454.35</t>
+          <t>10454.50</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
@@ -18883,12 +18883,12 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>-100.03</t>
+          <t>-100.05</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>685922189.8359375</t>
+          <t>599026183.8050847</t>
         </is>
       </c>
       <c r="BL35" t="inlineStr">
@@ -18928,12 +18928,12 @@
       </c>
       <c r="BQ35" t="inlineStr">
         <is>
-          <t>308332.2128302129</t>
+          <t>308332.2128152866</t>
         </is>
       </c>
       <c r="BR35" t="inlineStr">
         <is>
-          <t>-35169402.36628497</t>
+          <t>-35169402.36628824</t>
         </is>
       </c>
       <c r="BS35" t="inlineStr">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-01-09 00:00:00</t>
+          <t>2026-01-28 00:00:00</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>812372615.4853802</t>
+          <t>1541802024.607595</t>
         </is>
       </c>
       <c r="BL36" t="inlineStr">
@@ -19462,12 +19462,12 @@
       </c>
       <c r="BQ36" t="inlineStr">
         <is>
-          <t>-138086486.9732932</t>
+          <t>-138086486.9732901</t>
         </is>
       </c>
       <c r="BR36" t="inlineStr">
         <is>
-          <t>-217249562.9118428</t>
+          <t>-217249562.9118422</t>
         </is>
       </c>
       <c r="BS36" t="inlineStr">
@@ -19632,7 +19632,7 @@
       </c>
       <c r="CY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CZ36" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-01-23 00:00:00</t>
+          <t>2026-01-26 00:00:00</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="BK37" t="inlineStr">
         <is>
-          <t>1988100.512695312</t>
+          <t>3217243.125</t>
         </is>
       </c>
       <c r="BL37" t="inlineStr">
@@ -19998,12 +19998,12 @@
       </c>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>461743.0988745402</t>
+          <t>461743.0988745346</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
         <is>
-          <t>-23574.04191541485</t>
+          <t>-23574.04191541672</t>
         </is>
       </c>
       <c r="BS37" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -20245,7 +20245,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-30.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2025-09-08 00:00:00</t>
+          <t>2025-09-09 00:00:00</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>98.47999999999999</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -20488,12 +20488,12 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>-108.03</t>
+          <t>-122.58</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="BK38" t="inlineStr">
         <is>
-          <t>208754.4064327485</t>
+          <t>279677.8797468354</t>
         </is>
       </c>
       <c r="BL38" t="inlineStr">
@@ -20533,12 +20533,12 @@
       </c>
       <c r="BQ38" t="inlineStr">
         <is>
-          <t>-465.6259227003665</t>
+          <t>-465.6259227706917</t>
         </is>
       </c>
       <c r="BR38" t="inlineStr">
         <is>
-          <t>-1933.572837661217</t>
+          <t>-1933.572837676293</t>
         </is>
       </c>
       <c r="BS38" t="inlineStr">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="CR38" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
       <c r="CS38" t="inlineStr">
@@ -20765,7 +20765,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -20790,7 +20790,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-02-21 00:00:00</t>
+          <t>2026-02-22 00:00:00</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -20875,12 +20875,12 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2024/11/28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-02-10 00:00:00</t>
+          <t>2026-02-11 00:00:00</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
@@ -21020,12 +21020,12 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>-89.23</t>
+          <t>-88.99</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr">
@@ -21035,7 +21035,7 @@
       </c>
       <c r="BK39" t="inlineStr">
         <is>
-          <t>1794961506.621094</t>
+          <t>3080143145.329114</t>
         </is>
       </c>
       <c r="BL39" t="inlineStr">
@@ -21065,12 +21065,12 @@
       </c>
       <c r="BQ39" t="inlineStr">
         <is>
-          <t>21056306.24021269</t>
+          <t>21056306.24023474</t>
         </is>
       </c>
       <c r="BR39" t="inlineStr">
         <is>
-          <t>413114914.5748525</t>
+          <t>413114914.5748577</t>
         </is>
       </c>
       <c r="BS39" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="BT39" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="BU39" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-02-21 00:00:00</t>
+          <t>2026-02-22 00:00:00</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -21407,12 +21407,12 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2025/01/02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="BK40" t="inlineStr">
         <is>
-          <t>10674577358.4883</t>
+          <t>10696601959.93038</t>
         </is>
       </c>
       <c r="BL40" t="inlineStr">
@@ -21597,12 +21597,12 @@
       </c>
       <c r="BQ40" t="inlineStr">
         <is>
-          <t>492451658.5156305</t>
+          <t>492451658.5157425</t>
         </is>
       </c>
       <c r="BR40" t="inlineStr">
         <is>
-          <t>-305598602.7037659</t>
+          <t>-305598602.703743</t>
         </is>
       </c>
       <c r="BS40" t="inlineStr">
@@ -21612,7 +21612,7 @@
       </c>
       <c r="BT40" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="BU40" t="inlineStr">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2025-06-25 00:00:00</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -21859,17 +21859,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2025-06-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2025-06-16 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -21884,12 +21884,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-02-03 00:00:00</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>80.14000000000001</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
@@ -22084,12 +22084,12 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>-122.74</t>
+          <t>-122.96</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="BK41" t="inlineStr">
         <is>
-          <t>1464.333661417323</t>
+          <t>1356.935897435897</t>
         </is>
       </c>
       <c r="BL41" t="inlineStr">
@@ -22129,12 +22129,12 @@
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>-111.6708036097706</t>
+          <t>-111.6708036097623</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
         <is>
-          <t>-105.0508611205698</t>
+          <t>-105.050861120568</t>
         </is>
       </c>
       <c r="BS41" t="inlineStr">
@@ -22391,12 +22391,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2025-01-08 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-01-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -22416,12 +22416,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -22576,12 +22576,12 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>73.07</t>
+          <t>73.07000000000001</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>73.93</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>77.43400000000001</t>
+          <t>77.434</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
@@ -22616,12 +22616,12 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>-136.10</t>
+          <t>-161.79</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="BK42" t="inlineStr">
         <is>
-          <t>26870650.81690141</t>
+          <t>9192955.0</t>
         </is>
       </c>
       <c r="BL42" t="inlineStr">
@@ -22661,12 +22661,12 @@
       </c>
       <c r="BQ42" t="inlineStr">
         <is>
-          <t>-1307320.758141014</t>
+          <t>-1307320.758142424</t>
         </is>
       </c>
       <c r="BR42" t="inlineStr">
         <is>
-          <t>-613361.3855468575</t>
+          <t>-613361.3855471592</t>
         </is>
       </c>
       <c r="BS42" t="inlineStr">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-08-12 00:00:00</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
@@ -23148,12 +23148,12 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-120.54</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="BK43" t="inlineStr">
         <is>
-          <t>9757.982456140351</t>
+          <t>15194.76582278481</t>
         </is>
       </c>
       <c r="BL43" t="inlineStr">
@@ -23193,12 +23193,12 @@
       </c>
       <c r="BQ43" t="inlineStr">
         <is>
-          <t>38.77330843750699</t>
+          <t>38.77330843603244</t>
         </is>
       </c>
       <c r="BR43" t="inlineStr">
         <is>
-          <t>-123.5451157122889</t>
+          <t>-123.5451157126054</t>
         </is>
       </c>
       <c r="BS43" t="inlineStr">
@@ -23328,7 +23328,7 @@
       </c>
       <c r="CR43" t="inlineStr">
         <is>
-          <t>觀光事業平上櫃</t>
+          <t>觀光事業右下上櫃</t>
         </is>
       </c>
       <c r="CS43" t="inlineStr">
@@ -23565,7 +23565,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-10-09 00:00:00</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -23695,7 +23695,7 @@
       </c>
       <c r="BK44" t="inlineStr">
         <is>
-          <t>2720.847826086957</t>
+          <t>2284.965957446809</t>
         </is>
       </c>
       <c r="BL44" t="inlineStr">
@@ -23725,12 +23725,12 @@
       </c>
       <c r="BQ44" t="inlineStr">
         <is>
-          <t>73.28617007437046</t>
+          <t>73.28617007438189</t>
         </is>
       </c>
       <c r="BR44" t="inlineStr">
         <is>
-          <t>339.9421670555093</t>
+          <t>339.9421670555116</t>
         </is>
       </c>
       <c r="BS44" t="inlineStr">
@@ -23972,37 +23972,37 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-05-23 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2025-06-09 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2024-12-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2024-12-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>237.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -24027,12 +24027,12 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2025-08-13 00:00:00</t>
+          <t>2025-09-15 00:00:00</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
@@ -24212,12 +24212,12 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>-105.67</t>
+          <t>-105.72</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr">
@@ -24227,7 +24227,7 @@
       </c>
       <c r="BK45" t="inlineStr">
         <is>
-          <t>197749574.8304093</t>
+          <t>152385212.5759494</t>
         </is>
       </c>
       <c r="BL45" t="inlineStr">
@@ -24257,12 +24257,12 @@
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>-1205403.064542181</t>
+          <t>-1205403.064541849</t>
         </is>
       </c>
       <c r="BR45" t="inlineStr">
         <is>
-          <t>-3225626.184763141</t>
+          <t>-3225626.184763059</t>
         </is>
       </c>
       <c r="BS45" t="inlineStr">
@@ -24509,32 +24509,32 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-02-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2024-05-23 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2024-06-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -24544,12 +24544,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -24559,12 +24559,12 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>-12.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -24629,7 +24629,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2025-09-11 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
@@ -24744,12 +24744,12 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>-108.96</t>
+          <t>-125.63</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr">
@@ -24759,7 +24759,7 @@
       </c>
       <c r="BK46" t="inlineStr">
         <is>
-          <t>4111622.409356725</t>
+          <t>2319966.550632911</t>
         </is>
       </c>
       <c r="BL46" t="inlineStr">
@@ -24789,12 +24789,12 @@
       </c>
       <c r="BQ46" t="inlineStr">
         <is>
-          <t>65949.7503757228</t>
+          <t>65949.75037579043</t>
         </is>
       </c>
       <c r="BR46" t="inlineStr">
         <is>
-          <t>62563.41294332175</t>
+          <t>62563.41294333618</t>
         </is>
       </c>
       <c r="BS46" t="inlineStr">
@@ -25021,7 +25021,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -25051,12 +25051,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -25076,12 +25076,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>-15.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2025-08-08 00:00:00</t>
+          <t>2025-08-07 00:00:00</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -25297,7 +25297,7 @@
       </c>
       <c r="BK47" t="inlineStr">
         <is>
-          <t>427323282.6900585</t>
+          <t>377964916.113924</t>
         </is>
       </c>
       <c r="BL47" t="inlineStr">
@@ -25327,12 +25327,12 @@
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>-10694958.11543477</t>
+          <t>-10694958.1154364</t>
         </is>
       </c>
       <c r="BR47" t="inlineStr">
         <is>
-          <t>-19408141.31250763</t>
+          <t>-19408141.312508</t>
         </is>
       </c>
       <c r="BS47" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-02-21 00:00:00</t>
+          <t>2026-02-22 00:00:00</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -25639,12 +25639,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025/05/13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>674.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2025/03/27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>595.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-01-23 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -25829,7 +25829,7 @@
       </c>
       <c r="BK48" t="inlineStr">
         <is>
-          <t>5999489251.777778</t>
+          <t>7583305750.601266</t>
         </is>
       </c>
       <c r="BL48" t="inlineStr">
@@ -25859,12 +25859,12 @@
       </c>
       <c r="BQ48" t="inlineStr">
         <is>
-          <t>546085505.8938491</t>
+          <t>546085505.8939428</t>
         </is>
       </c>
       <c r="BR48" t="inlineStr">
         <is>
-          <t>687894794.9043465</t>
+          <t>687894794.9043655</t>
         </is>
       </c>
       <c r="BS48" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="BT48" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="BU48" t="inlineStr">
@@ -26091,7 +26091,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -26106,7 +26106,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-02-21 00:00:00</t>
+          <t>2026-02-22 00:00:00</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -26171,12 +26171,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025/05/15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -26201,12 +26201,12 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2025/02/13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>226.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2026-01-29 00:00:00</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
@@ -26361,7 +26361,7 @@
       </c>
       <c r="BK49" t="inlineStr">
         <is>
-          <t>4502374214.467836</t>
+          <t>6646496292.120253</t>
         </is>
       </c>
       <c r="BL49" t="inlineStr">
@@ -26391,12 +26391,12 @@
       </c>
       <c r="BQ49" t="inlineStr">
         <is>
-          <t>243739929.6897047</t>
+          <t>243739929.6897638</t>
         </is>
       </c>
       <c r="BR49" t="inlineStr">
         <is>
-          <t>355155423.589777</t>
+          <t>355155423.5897894</t>
         </is>
       </c>
       <c r="BS49" t="inlineStr">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="BT49" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="BU49" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2026-01-21 00:00:00</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
@@ -26878,12 +26878,12 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>-88.04</t>
+          <t>-53.94</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="BK50" t="inlineStr">
         <is>
-          <t>1495735283.18504</t>
+          <t>609604770.7341772</t>
         </is>
       </c>
       <c r="BL50" t="inlineStr">
@@ -26923,12 +26923,12 @@
       </c>
       <c r="BQ50" t="inlineStr">
         <is>
-          <t>7702484.281969444</t>
+          <t>7702484.281963001</t>
         </is>
       </c>
       <c r="BR50" t="inlineStr">
         <is>
-          <t>-41688492.54222143</t>
+          <t>-41688492.54222286</t>
         </is>
       </c>
       <c r="BS50" t="inlineStr">
@@ -27058,7 +27058,7 @@
       </c>
       <c r="CR50" t="inlineStr">
         <is>
-          <t>半導體業平上市</t>
+          <t>半導體業右上上市</t>
         </is>
       </c>
       <c r="CS50" t="inlineStr">
@@ -27155,7 +27155,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -27170,179 +27170,179 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-02-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-02-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1305.0</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1305.0</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1265.0</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1215.0</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>7.41</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025/05/19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>705.0</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>960.0</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>1215.0</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>2026/01/02</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>1145.0</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>2026-02-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>45.87</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>通信網路｜下游｜網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>7613</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2026-02-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2026-01-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>1305.0</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>1305.0</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>1265.0</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>1215.0</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>7.41</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2025/05/19</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>705.0</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>960.0</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>2025/02/20</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>1215.0</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>2026/01/02</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>1145.0</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>2026-02-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>45.87</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP51" t="inlineStr">
-        <is>
-          <t>通信網路｜下游｜網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>7613</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
+      <c r="AT51" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AT51" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="AU51" t="inlineStr">
         <is>
           <t>12.23</t>
@@ -27410,7 +27410,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>60.81</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
@@ -27425,7 +27425,7 @@
       </c>
       <c r="BK51" t="inlineStr">
         <is>
-          <t>5335415354.391813</t>
+          <t>7276135341.322784</t>
         </is>
       </c>
       <c r="BL51" t="inlineStr">
@@ -27455,12 +27455,12 @@
       </c>
       <c r="BQ51" t="inlineStr">
         <is>
-          <t>186186662.2342147</t>
+          <t>186186662.2342376</t>
         </is>
       </c>
       <c r="BR51" t="inlineStr">
         <is>
-          <t>933243518.2280722</t>
+          <t>933243518.2280769</t>
         </is>
       </c>
       <c r="BS51" t="inlineStr">
@@ -27470,7 +27470,7 @@
       </c>
       <c r="BT51" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="BU51" t="inlineStr">
@@ -27687,7 +27687,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -27702,7 +27702,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -27797,12 +27797,12 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-02-11 00:00:00</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
@@ -28015,7 +28015,7 @@
       </c>
       <c r="BK52" t="inlineStr">
         <is>
-          <t>9050099407.760235</t>
+          <t>13161779506.31013</t>
         </is>
       </c>
       <c r="BL52" t="inlineStr">
@@ -28045,12 +28045,12 @@
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
-          <t>54374674.64593329</t>
+          <t>54374674.64585207</t>
         </is>
       </c>
       <c r="BR52" t="inlineStr">
         <is>
-          <t>-114301148.5345879</t>
+          <t>-114301148.5346069</t>
         </is>
       </c>
       <c r="BS52" t="inlineStr">
@@ -28215,7 +28215,7 @@
       </c>
       <c r="CY52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CZ52" t="inlineStr">
@@ -28277,7 +28277,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -28357,12 +28357,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025/02/18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>1855.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -28387,12 +28387,12 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2025/04/11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>1455.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
@@ -28417,7 +28417,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>2026-01-20 00:00:00</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
@@ -28533,12 +28533,12 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>200.81</t>
+          <t>200.76</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>-155.88</t>
+          <t>-155.89</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="BK53" t="inlineStr">
         <is>
-          <t>3090113405.426901</t>
+          <t>3782220887.240506</t>
         </is>
       </c>
       <c r="BL53" t="inlineStr">
@@ -28578,12 +28578,12 @@
       </c>
       <c r="BQ53" t="inlineStr">
         <is>
-          <t>-90285100.01353636</t>
+          <t>-90285100.01350772</t>
         </is>
       </c>
       <c r="BR53" t="inlineStr">
         <is>
-          <t>-233676392.1679134</t>
+          <t>-233676392.1679072</t>
         </is>
       </c>
       <c r="BS53" t="inlineStr">
@@ -28598,17 +28598,17 @@
       </c>
       <c r="BU53" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV53" t="inlineStr">
         <is>
-          <t>2025/05/15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW53" t="inlineStr">
         <is>
-          <t>51.50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX53" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="CR53" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CS53" t="inlineStr">
